--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE7CA6D-5C92-441D-B56C-DC09962B5937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC284C4A-2A9D-4CEB-9206-1C51106AA5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="28" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="170">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -640,6 +640,9 @@
   <si>
     <t>Bakytzhan Suleimenov (UCC, bsuleimenov@ucc.ie)</t>
   </si>
+  <si>
+    <t>P24</t>
+  </si>
 </sst>
 </file>
 
@@ -648,7 +651,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -837,6 +840,10 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1556,7 +1563,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>28575</xdr:colOff>
+          <xdr:colOff>30480</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -4005,21 +4012,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3D08AF-561B-4741-93FB-876D250B4223}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="21.7109375" style="42" customWidth="1"/>
-    <col min="5" max="6" width="14.140625" style="42" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="42" customWidth="1"/>
-    <col min="8" max="10" width="8.140625" style="42" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" style="42" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" style="42" customWidth="1"/>
+    <col min="1" max="4" width="21.6640625" style="42" customWidth="1"/>
+    <col min="5" max="6" width="14.109375" style="42" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="42" customWidth="1"/>
+    <col min="8" max="10" width="8.109375" style="42" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="42" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" style="42" customWidth="1"/>
     <col min="13" max="13" width="10" style="42" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="42" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="42" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="42"/>
+    <col min="14" max="14" width="11.44140625" style="42" customWidth="1"/>
+    <col min="15" max="15" width="13.44140625" style="42" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="40"/>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -4047,7 +4054,7 @@
       <c r="Y1" s="41"/>
       <c r="Z1" s="41"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -4075,7 +4082,7 @@
       <c r="Y2" s="41"/>
       <c r="Z2" s="41"/>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" s="40"/>
       <c r="B3" s="40"/>
       <c r="C3" s="40"/>
@@ -4103,7 +4110,7 @@
       <c r="Y3" s="41"/>
       <c r="Z3" s="41"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="40"/>
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
@@ -4131,7 +4138,7 @@
       <c r="Y4" s="41"/>
       <c r="Z4" s="41"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="40"/>
       <c r="B5" s="40"/>
       <c r="C5" s="40"/>
@@ -4159,7 +4166,7 @@
       <c r="Y5" s="41"/>
       <c r="Z5" s="41"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="40"/>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
@@ -4187,7 +4194,7 @@
       <c r="Y6" s="41"/>
       <c r="Z6" s="41"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="40"/>
       <c r="B7" s="40"/>
       <c r="C7" s="40"/>
@@ -4215,7 +4222,7 @@
       <c r="Y7" s="41"/>
       <c r="Z7" s="41"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="40"/>
       <c r="B8" s="40"/>
       <c r="C8" s="40"/>
@@ -4243,7 +4250,7 @@
       <c r="Y8" s="41"/>
       <c r="Z8" s="41"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" s="40"/>
       <c r="B9" s="40"/>
       <c r="C9" s="40"/>
@@ -4271,7 +4278,7 @@
       <c r="Y9" s="41"/>
       <c r="Z9" s="41"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" s="40"/>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
@@ -4299,7 +4306,7 @@
       <c r="Y10" s="41"/>
       <c r="Z10" s="41"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" s="40"/>
       <c r="B11" s="40"/>
       <c r="C11" s="40"/>
@@ -4327,7 +4334,7 @@
       <c r="Y11" s="41"/>
       <c r="Z11" s="41"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" s="40"/>
       <c r="B12" s="40"/>
       <c r="C12" s="40"/>
@@ -4355,7 +4362,7 @@
       <c r="Y12" s="41"/>
       <c r="Z12" s="41"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" s="40"/>
       <c r="B13" s="40"/>
       <c r="C13" s="40"/>
@@ -4383,7 +4390,7 @@
       <c r="Y13" s="41"/>
       <c r="Z13" s="41"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" s="40"/>
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
@@ -4411,7 +4418,7 @@
       <c r="Y14" s="41"/>
       <c r="Z14" s="41"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="40"/>
       <c r="B15" s="40"/>
       <c r="C15" s="40"/>
@@ -4439,7 +4446,7 @@
       <c r="Y15" s="41"/>
       <c r="Z15" s="41"/>
     </row>
-    <row r="16" spans="1:26" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="102.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="57" t="s">
         <v>144</v>
       </c>
@@ -4469,7 +4476,7 @@
       <c r="Y16" s="41"/>
       <c r="Z16" s="41"/>
     </row>
-    <row r="17" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="45"/>
       <c r="B17" s="45"/>
       <c r="C17" s="45"/>
@@ -4497,7 +4504,7 @@
       <c r="Y17" s="41"/>
       <c r="Z17" s="41"/>
     </row>
-    <row r="18" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="45"/>
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
@@ -4525,7 +4532,7 @@
       <c r="Y18" s="41"/>
       <c r="Z18" s="41"/>
     </row>
-    <row r="19" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48" t="s">
         <v>145</v>
       </c>
@@ -4557,7 +4564,7 @@
       <c r="Y19" s="41"/>
       <c r="Z19" s="41"/>
     </row>
-    <row r="20" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="48" t="s">
         <v>146</v>
       </c>
@@ -4589,7 +4596,7 @@
       <c r="Y20" s="41"/>
       <c r="Z20" s="41"/>
     </row>
-    <row r="21" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48" t="s">
         <v>147</v>
       </c>
@@ -4621,7 +4628,7 @@
       <c r="Y21" s="41"/>
       <c r="Z21" s="41"/>
     </row>
-    <row r="22" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48"/>
       <c r="B22" s="51"/>
       <c r="C22" s="51"/>
@@ -4649,7 +4656,7 @@
       <c r="Y22" s="41"/>
       <c r="Z22" s="41"/>
     </row>
-    <row r="23" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="48" t="s">
         <v>148</v>
       </c>
@@ -4681,7 +4688,7 @@
       <c r="Y23" s="41"/>
       <c r="Z23" s="41"/>
     </row>
-    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="48"/>
       <c r="B24" s="51" t="s">
         <v>159</v>
@@ -4711,7 +4718,7 @@
       <c r="Y24" s="41"/>
       <c r="Z24" s="41"/>
     </row>
-    <row r="25" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="48"/>
       <c r="B25" s="51"/>
       <c r="C25" s="51"/>
@@ -4739,7 +4746,7 @@
       <c r="Y25" s="41"/>
       <c r="Z25" s="41"/>
     </row>
-    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="48" t="s">
         <v>149</v>
       </c>
@@ -4771,7 +4778,7 @@
       <c r="Y26" s="41"/>
       <c r="Z26" s="41"/>
     </row>
-    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="48"/>
       <c r="B27" s="51"/>
       <c r="C27" s="51"/>
@@ -4799,7 +4806,7 @@
       <c r="Y27" s="41"/>
       <c r="Z27" s="41"/>
     </row>
-    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="48"/>
       <c r="B28" s="51"/>
       <c r="C28" s="51"/>
@@ -4827,7 +4834,7 @@
       <c r="Y28" s="41"/>
       <c r="Z28" s="41"/>
     </row>
-    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="48" t="s">
         <v>150</v>
       </c>
@@ -4859,7 +4866,7 @@
       <c r="Y29" s="41"/>
       <c r="Z29" s="41"/>
     </row>
-    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="48" t="s">
         <v>151</v>
       </c>
@@ -4891,7 +4898,7 @@
       <c r="Y30" s="41"/>
       <c r="Z30" s="41"/>
     </row>
-    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="48" t="s">
         <v>153</v>
       </c>
@@ -4923,7 +4930,7 @@
       <c r="Y31" s="41"/>
       <c r="Z31" s="41"/>
     </row>
-    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="54"/>
       <c r="B32" s="55" t="s">
         <v>155</v>
@@ -4953,7 +4960,7 @@
       <c r="Y32" s="41"/>
       <c r="Z32" s="41"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A33" s="40"/>
       <c r="B33" s="40"/>
       <c r="C33" s="40"/>
@@ -4981,7 +4988,7 @@
       <c r="Y33" s="41"/>
       <c r="Z33" s="41"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A34" s="40"/>
       <c r="B34" s="40"/>
       <c r="C34" s="40"/>
@@ -5009,7 +5016,7 @@
       <c r="Y34" s="41"/>
       <c r="Z34" s="41"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A35" s="40"/>
       <c r="B35" s="40"/>
       <c r="C35" s="40"/>
@@ -5037,7 +5044,7 @@
       <c r="Y35" s="41"/>
       <c r="Z35" s="41"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A36" s="40"/>
       <c r="B36" s="40"/>
       <c r="C36" s="40"/>
@@ -5065,7 +5072,7 @@
       <c r="Y36" s="41"/>
       <c r="Z36" s="41"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A37" s="40"/>
       <c r="B37" s="40"/>
       <c r="C37" s="40"/>
@@ -5093,7 +5100,7 @@
       <c r="Y37" s="41"/>
       <c r="Z37" s="41"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A38" s="40"/>
       <c r="B38" s="40"/>
       <c r="C38" s="40"/>
@@ -5121,7 +5128,7 @@
       <c r="Y38" s="41"/>
       <c r="Z38" s="41"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A39" s="40"/>
       <c r="B39" s="40"/>
       <c r="C39" s="40"/>
@@ -5149,7 +5156,7 @@
       <c r="Y39" s="41"/>
       <c r="Z39" s="41"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A40" s="40"/>
       <c r="B40" s="40"/>
       <c r="C40" s="40"/>
@@ -5177,7 +5184,7 @@
       <c r="Y40" s="41"/>
       <c r="Z40" s="41"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A41" s="40"/>
       <c r="B41" s="40"/>
       <c r="C41" s="40"/>
@@ -5205,7 +5212,7 @@
       <c r="Y41" s="41"/>
       <c r="Z41" s="41"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A42" s="40"/>
       <c r="B42" s="40"/>
       <c r="C42" s="40"/>
@@ -5233,7 +5240,7 @@
       <c r="Y42" s="41"/>
       <c r="Z42" s="41"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A43" s="41"/>
       <c r="B43" s="41"/>
       <c r="C43" s="41"/>
@@ -5261,7 +5268,7 @@
       <c r="Y43" s="41"/>
       <c r="Z43" s="41"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A44" s="41"/>
       <c r="B44" s="41"/>
       <c r="C44" s="41"/>
@@ -5289,7 +5296,7 @@
       <c r="Y44" s="41"/>
       <c r="Z44" s="41"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A45" s="41"/>
       <c r="B45" s="41"/>
       <c r="C45" s="41"/>
@@ -5317,7 +5324,7 @@
       <c r="Y45" s="41"/>
       <c r="Z45" s="41"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A46" s="41"/>
       <c r="B46" s="41"/>
       <c r="C46" s="41"/>
@@ -5345,7 +5352,7 @@
       <c r="Y46" s="41"/>
       <c r="Z46" s="41"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A47" s="41"/>
       <c r="B47" s="41"/>
       <c r="C47" s="41"/>
@@ -5373,7 +5380,7 @@
       <c r="Y47" s="41"/>
       <c r="Z47" s="41"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A48" s="41"/>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
@@ -5401,7 +5408,7 @@
       <c r="Y48" s="41"/>
       <c r="Z48" s="41"/>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A49" s="41"/>
       <c r="B49" s="41"/>
       <c r="C49" s="41"/>
@@ -5429,7 +5436,7 @@
       <c r="Y49" s="41"/>
       <c r="Z49" s="41"/>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A50" s="41"/>
       <c r="B50" s="41"/>
       <c r="C50" s="41"/>
@@ -5457,7 +5464,7 @@
       <c r="Y50" s="41"/>
       <c r="Z50" s="41"/>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A51" s="41"/>
       <c r="B51" s="41"/>
       <c r="C51" s="41"/>
@@ -5485,7 +5492,7 @@
       <c r="Y51" s="41"/>
       <c r="Z51" s="41"/>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A52" s="41"/>
       <c r="B52" s="41"/>
       <c r="C52" s="41"/>
@@ -5513,7 +5520,7 @@
       <c r="Y52" s="41"/>
       <c r="Z52" s="41"/>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A53" s="41"/>
       <c r="B53" s="41"/>
       <c r="C53" s="41"/>
@@ -5541,7 +5548,7 @@
       <c r="Y53" s="41"/>
       <c r="Z53" s="41"/>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A54" s="41"/>
       <c r="B54" s="41"/>
       <c r="C54" s="41"/>
@@ -5569,7 +5576,7 @@
       <c r="Y54" s="41"/>
       <c r="Z54" s="41"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A55" s="41"/>
       <c r="B55" s="41"/>
       <c r="C55" s="41"/>
@@ -5597,7 +5604,7 @@
       <c r="Y55" s="41"/>
       <c r="Z55" s="41"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A56" s="41"/>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -5625,7 +5632,7 @@
       <c r="Y56" s="41"/>
       <c r="Z56" s="41"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A57" s="41"/>
       <c r="B57" s="41"/>
       <c r="C57" s="41"/>
@@ -5653,7 +5660,7 @@
       <c r="Y57" s="41"/>
       <c r="Z57" s="41"/>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A58" s="41"/>
       <c r="B58" s="41"/>
       <c r="C58" s="41"/>
@@ -5681,7 +5688,7 @@
       <c r="Y58" s="41"/>
       <c r="Z58" s="41"/>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A59" s="41"/>
       <c r="B59" s="41"/>
       <c r="C59" s="41"/>
@@ -5709,7 +5716,7 @@
       <c r="Y59" s="41"/>
       <c r="Z59" s="41"/>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A60" s="41"/>
       <c r="B60" s="41"/>
       <c r="C60" s="41"/>
@@ -5737,7 +5744,7 @@
       <c r="Y60" s="41"/>
       <c r="Z60" s="41"/>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A61" s="41"/>
       <c r="B61" s="41"/>
       <c r="C61" s="41"/>
@@ -5765,7 +5772,7 @@
       <c r="Y61" s="41"/>
       <c r="Z61" s="41"/>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A62" s="41"/>
       <c r="B62" s="41"/>
       <c r="C62" s="41"/>
@@ -5793,7 +5800,7 @@
       <c r="Y62" s="41"/>
       <c r="Z62" s="41"/>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A63" s="41"/>
       <c r="B63" s="41"/>
       <c r="C63" s="41"/>
@@ -5821,7 +5828,7 @@
       <c r="Y63" s="41"/>
       <c r="Z63" s="41"/>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A64" s="41"/>
       <c r="B64" s="41"/>
       <c r="C64" s="41"/>
@@ -5849,7 +5856,7 @@
       <c r="Y64" s="41"/>
       <c r="Z64" s="41"/>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A65" s="41"/>
       <c r="B65" s="41"/>
       <c r="C65" s="41"/>
@@ -5877,7 +5884,7 @@
       <c r="Y65" s="41"/>
       <c r="Z65" s="41"/>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A66" s="41"/>
       <c r="B66" s="41"/>
       <c r="C66" s="41"/>
@@ -5905,7 +5912,7 @@
       <c r="Y66" s="41"/>
       <c r="Z66" s="41"/>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A67" s="41"/>
       <c r="B67" s="41"/>
       <c r="C67" s="41"/>
@@ -5933,7 +5940,7 @@
       <c r="Y67" s="41"/>
       <c r="Z67" s="41"/>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A68" s="41"/>
       <c r="B68" s="41"/>
       <c r="C68" s="41"/>
@@ -5961,7 +5968,7 @@
       <c r="Y68" s="41"/>
       <c r="Z68" s="41"/>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A69" s="41"/>
       <c r="B69" s="41"/>
       <c r="C69" s="41"/>
@@ -5989,7 +5996,7 @@
       <c r="Y69" s="41"/>
       <c r="Z69" s="41"/>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A70" s="41"/>
       <c r="B70" s="41"/>
       <c r="C70" s="41"/>
@@ -6017,7 +6024,7 @@
       <c r="Y70" s="41"/>
       <c r="Z70" s="41"/>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A71" s="41"/>
       <c r="B71" s="41"/>
       <c r="C71" s="41"/>
@@ -6045,7 +6052,7 @@
       <c r="Y71" s="41"/>
       <c r="Z71" s="41"/>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A72" s="41"/>
       <c r="B72" s="41"/>
       <c r="C72" s="41"/>
@@ -6073,7 +6080,7 @@
       <c r="Y72" s="41"/>
       <c r="Z72" s="41"/>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A73" s="41"/>
       <c r="B73" s="41"/>
       <c r="C73" s="41"/>
@@ -6101,7 +6108,7 @@
       <c r="Y73" s="41"/>
       <c r="Z73" s="41"/>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A74" s="41"/>
       <c r="B74" s="41"/>
       <c r="C74" s="41"/>
@@ -6129,7 +6136,7 @@
       <c r="Y74" s="41"/>
       <c r="Z74" s="41"/>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A75" s="41"/>
       <c r="B75" s="41"/>
       <c r="C75" s="41"/>
@@ -6157,7 +6164,7 @@
       <c r="Y75" s="41"/>
       <c r="Z75" s="41"/>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A76" s="41"/>
       <c r="B76" s="41"/>
       <c r="C76" s="41"/>
@@ -6185,7 +6192,7 @@
       <c r="Y76" s="41"/>
       <c r="Z76" s="41"/>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A77" s="41"/>
       <c r="B77" s="41"/>
       <c r="C77" s="41"/>
@@ -6213,7 +6220,7 @@
       <c r="Y77" s="41"/>
       <c r="Z77" s="41"/>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A78" s="41"/>
       <c r="B78" s="41"/>
       <c r="C78" s="41"/>
@@ -6241,7 +6248,7 @@
       <c r="Y78" s="41"/>
       <c r="Z78" s="41"/>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A79" s="41"/>
       <c r="B79" s="41"/>
       <c r="C79" s="41"/>
@@ -6269,7 +6276,7 @@
       <c r="Y79" s="41"/>
       <c r="Z79" s="41"/>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A80" s="41"/>
       <c r="B80" s="41"/>
       <c r="C80" s="41"/>
@@ -6297,7 +6304,7 @@
       <c r="Y80" s="41"/>
       <c r="Z80" s="41"/>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A81" s="41"/>
       <c r="B81" s="41"/>
       <c r="C81" s="41"/>
@@ -6325,7 +6332,7 @@
       <c r="Y81" s="41"/>
       <c r="Z81" s="41"/>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A82" s="41"/>
       <c r="B82" s="41"/>
       <c r="C82" s="41"/>
@@ -6353,7 +6360,7 @@
       <c r="Y82" s="41"/>
       <c r="Z82" s="41"/>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A83" s="41"/>
       <c r="B83" s="41"/>
       <c r="C83" s="41"/>
@@ -6381,7 +6388,7 @@
       <c r="Y83" s="41"/>
       <c r="Z83" s="41"/>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A84" s="41"/>
       <c r="B84" s="41"/>
       <c r="C84" s="41"/>
@@ -6409,7 +6416,7 @@
       <c r="Y84" s="41"/>
       <c r="Z84" s="41"/>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A85" s="41"/>
       <c r="B85" s="41"/>
       <c r="C85" s="41"/>
@@ -6437,7 +6444,7 @@
       <c r="Y85" s="41"/>
       <c r="Z85" s="41"/>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A86" s="41"/>
       <c r="B86" s="41"/>
       <c r="C86" s="41"/>
@@ -6465,7 +6472,7 @@
       <c r="Y86" s="41"/>
       <c r="Z86" s="41"/>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A87" s="41"/>
       <c r="B87" s="41"/>
       <c r="C87" s="41"/>
@@ -6493,7 +6500,7 @@
       <c r="Y87" s="41"/>
       <c r="Z87" s="41"/>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A88" s="41"/>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -6521,7 +6528,7 @@
       <c r="Y88" s="41"/>
       <c r="Z88" s="41"/>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A89" s="41"/>
       <c r="B89" s="41"/>
       <c r="C89" s="41"/>
@@ -6549,7 +6556,7 @@
       <c r="Y89" s="41"/>
       <c r="Z89" s="41"/>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A90" s="41"/>
       <c r="B90" s="41"/>
       <c r="C90" s="41"/>
@@ -6577,7 +6584,7 @@
       <c r="Y90" s="41"/>
       <c r="Z90" s="41"/>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A91" s="41"/>
       <c r="B91" s="41"/>
       <c r="C91" s="41"/>
@@ -6605,7 +6612,7 @@
       <c r="Y91" s="41"/>
       <c r="Z91" s="41"/>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A92" s="41"/>
       <c r="B92" s="41"/>
       <c r="C92" s="41"/>
@@ -6633,7 +6640,7 @@
       <c r="Y92" s="41"/>
       <c r="Z92" s="41"/>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A93" s="41"/>
       <c r="B93" s="41"/>
       <c r="C93" s="41"/>
@@ -6661,7 +6668,7 @@
       <c r="Y93" s="41"/>
       <c r="Z93" s="41"/>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A94" s="41"/>
       <c r="B94" s="41"/>
       <c r="C94" s="41"/>
@@ -6689,7 +6696,7 @@
       <c r="Y94" s="41"/>
       <c r="Z94" s="41"/>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A95" s="41"/>
       <c r="B95" s="41"/>
       <c r="C95" s="41"/>
@@ -6717,7 +6724,7 @@
       <c r="Y95" s="41"/>
       <c r="Z95" s="41"/>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A96" s="41"/>
       <c r="B96" s="41"/>
       <c r="C96" s="41"/>
@@ -6745,7 +6752,7 @@
       <c r="Y96" s="41"/>
       <c r="Z96" s="41"/>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A97" s="41"/>
       <c r="B97" s="41"/>
       <c r="C97" s="41"/>
@@ -6773,7 +6780,7 @@
       <c r="Y97" s="41"/>
       <c r="Z97" s="41"/>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A98" s="41"/>
       <c r="B98" s="41"/>
       <c r="C98" s="41"/>
@@ -6801,7 +6808,7 @@
       <c r="Y98" s="41"/>
       <c r="Z98" s="41"/>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A99" s="41"/>
       <c r="B99" s="41"/>
       <c r="C99" s="41"/>
@@ -6853,38 +6860,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:AD37"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="3.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" customWidth="1"/>
-    <col min="10" max="11" width="5.7109375" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.44140625" customWidth="1"/>
+    <col min="10" max="11" width="5.6640625" customWidth="1"/>
+    <col min="12" max="12" width="6.5546875" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" customWidth="1"/>
+    <col min="14" max="14" width="6.6640625" customWidth="1"/>
+    <col min="15" max="15" width="6.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.109375" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="5.85546875" customWidth="1"/>
-    <col min="20" max="20" width="5.5703125" customWidth="1"/>
-    <col min="21" max="21" width="5.85546875" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" customWidth="1"/>
+    <col min="19" max="19" width="5.88671875" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" customWidth="1"/>
+    <col min="21" max="21" width="5.88671875" customWidth="1"/>
+    <col min="22" max="22" width="6.6640625" customWidth="1"/>
     <col min="23" max="23" width="5" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" customWidth="1"/>
+    <col min="24" max="24" width="7.5546875" customWidth="1"/>
+    <col min="25" max="25" width="6.6640625" customWidth="1"/>
     <col min="26" max="28" width="6" customWidth="1"/>
-    <col min="29" max="29" width="5.7109375" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" customWidth="1"/>
+    <col min="29" max="29" width="5.6640625" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="2" t="str">
         <f t="array" ref="C3">IF(INDEX(C5:C7,$A$4)&lt;&gt;0,INDEX(C5:C7,$A$4),"")</f>
         <v>IE</v>
@@ -6998,13 +7005,13 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>60</v>
       </c>
@@ -7119,7 +7126,7 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>62</v>
       </c>
@@ -7155,7 +7162,7 @@
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
     </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>63</v>
       </c>
@@ -7269,7 +7276,7 @@
       </c>
       <c r="AD7" s="2"/>
     </row>
-    <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>64</v>
       </c>
@@ -7277,7 +7284,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>66</v>
       </c>
@@ -7285,7 +7292,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>68</v>
       </c>
@@ -7293,7 +7300,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>70</v>
       </c>
@@ -7301,7 +7308,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>72</v>
       </c>
@@ -7309,7 +7316,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>74</v>
       </c>
@@ -7317,7 +7324,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>76</v>
       </c>
@@ -7325,7 +7332,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>78</v>
       </c>
@@ -7333,7 +7340,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>80</v>
       </c>
@@ -7341,7 +7348,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>82</v>
       </c>
@@ -7349,7 +7356,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>84</v>
       </c>
@@ -7357,7 +7364,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>86</v>
       </c>
@@ -7365,7 +7372,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>88</v>
       </c>
@@ -7373,7 +7380,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>90</v>
       </c>
@@ -7381,7 +7388,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>92</v>
       </c>
@@ -7389,7 +7396,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>94</v>
       </c>
@@ -7397,7 +7404,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>96</v>
       </c>
@@ -7405,7 +7412,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>98</v>
       </c>
@@ -7413,7 +7420,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>100</v>
       </c>
@@ -7421,7 +7428,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>102</v>
       </c>
@@ -7429,7 +7436,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>104</v>
       </c>
@@ -7437,7 +7444,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>106</v>
       </c>
@@ -7445,7 +7452,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>108</v>
       </c>
@@ -7453,7 +7460,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>110</v>
       </c>
@@ -7461,7 +7468,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>112</v>
       </c>
@@ -7469,7 +7476,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>114</v>
       </c>
@@ -7477,7 +7484,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>116</v>
       </c>
@@ -7485,7 +7492,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>118</v>
       </c>
@@ -7511,7 +7518,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>28575</xdr:colOff>
+                    <xdr:colOff>30480</xdr:colOff>
                     <xdr:row>3</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -7530,20 +7537,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A3:C39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="1" max="2" width="11.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
       <c r="B4" s="9" t="s">
         <v>8</v>
@@ -7552,7 +7559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="8" t="s">
         <v>33</v>
@@ -7562,7 +7569,7 @@
         <v>IE</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="str">
@@ -7570,7 +7577,7 @@
         <v>National</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="str">
@@ -7578,7 +7585,7 @@
         <v>IE-CW</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8" t="str">
@@ -7586,7 +7593,7 @@
         <v>IE-D</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8" t="str">
@@ -7594,7 +7601,7 @@
         <v>IE-KE</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8" t="str">
@@ -7602,7 +7609,7 @@
         <v>IE-KK</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8" t="str">
@@ -7610,7 +7617,7 @@
         <v>IE-LS</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8" t="str">
@@ -7618,7 +7625,7 @@
         <v>IE-LD</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="8" t="str">
@@ -7626,7 +7633,7 @@
         <v>IE-LH</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8" t="str">
@@ -7634,7 +7641,7 @@
         <v>IE-MH</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="8" t="str">
@@ -7642,7 +7649,7 @@
         <v>IE-OY</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="8" t="str">
@@ -7650,7 +7657,7 @@
         <v>IE-WH</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8" t="str">
@@ -7658,7 +7665,7 @@
         <v>IE-WX</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="8" t="str">
@@ -7666,7 +7673,7 @@
         <v>IE-WW</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8" t="str">
@@ -7674,116 +7681,116 @@
         <v>IE-CE</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="C20" s="8" t="str">
         <f>Regions!R3</f>
         <v>IE-CO</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="C21" s="8" t="str">
         <f>Regions!S3</f>
         <v>IE-KY</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="C22" s="8" t="str">
         <f>Regions!T3</f>
         <v>IE-LK</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="C23" s="8" t="str">
         <f>Regions!U3</f>
         <v>IE-TA</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="C24" s="8" t="str">
         <f>Regions!V3</f>
         <v>IE-WD</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
       <c r="C25" s="8" t="str">
         <f>Regions!W3</f>
         <v>IE-G</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
       <c r="C26" s="8" t="str">
         <f>Regions!X3</f>
         <v>IE-LM</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="C27" s="8" t="str">
         <f>Regions!Y3</f>
         <v>IE-MO</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
       <c r="C28" s="8" t="str">
         <f>Regions!Z3</f>
         <v>IE-RN</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
       <c r="C29" s="8" t="str">
         <f>Regions!AA3</f>
         <v>IE-SO</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="C30" s="8" t="str">
         <f>Regions!AB3</f>
         <v>IE-CN</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="7"/>
       <c r="C31" s="8" t="str">
         <f>Regions!AC3</f>
         <v>IE-DL</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
       <c r="C32" s="8" t="str">
         <f>Regions!AD3</f>
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="7"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
     </row>
   </sheetData>
@@ -7796,41 +7803,41 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B3:U51"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B3:V51"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="9" width="13.7109375" customWidth="1"/>
+    <col min="2" max="9" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="11"/>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2018</v>
       </c>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="11"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="11"/>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
         <v>137</v>
       </c>
@@ -7858,6 +7865,9 @@
       <c r="J12" s="13" t="s">
         <v>167</v>
       </c>
+      <c r="K12" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="M12" s="13" t="s">
         <v>137</v>
       </c>
@@ -7885,8 +7895,11 @@
       <c r="U12" s="13" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>1</v>
       </c>
@@ -7912,6 +7925,9 @@
         <v>1</v>
       </c>
       <c r="J13" s="12">
+        <v>1</v>
+      </c>
+      <c r="K13" s="12">
         <v>1</v>
       </c>
       <c r="M13" s="12">
@@ -7947,11 +7963,15 @@
         <v>2018</v>
       </c>
       <c r="U13" s="17">
-        <f t="shared" ref="U13" si="1">+T13</f>
+        <f t="shared" ref="U13:V13" si="1">+T13</f>
         <v>2018</v>
       </c>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="17">
+        <f t="shared" si="1"/>
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="12">
         <v>1</v>
       </c>
@@ -7977,6 +7997,9 @@
         <v>1</v>
       </c>
       <c r="J14" s="12">
+        <v>1</v>
+      </c>
+      <c r="K14" s="12">
         <v>1</v>
       </c>
       <c r="M14" s="12">
@@ -7984,7 +8007,7 @@
         <v>2019</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" ref="N14:U29" si="2">+N13+C14</f>
+        <f t="shared" ref="N14:V29" si="2">+N13+C14</f>
         <v>2019</v>
       </c>
       <c r="O14" s="12">
@@ -8015,8 +8038,12 @@
         <f t="shared" si="2"/>
         <v>2019</v>
       </c>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="17">
+        <f t="shared" si="2"/>
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>1</v>
       </c>
@@ -8042,6 +8069,9 @@
         <v>1</v>
       </c>
       <c r="J15" s="12">
+        <v>1</v>
+      </c>
+      <c r="K15" s="12">
         <v>1</v>
       </c>
       <c r="M15" s="12">
@@ -8080,8 +8110,12 @@
         <f t="shared" si="2"/>
         <v>2020</v>
       </c>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="17">
+        <f t="shared" si="2"/>
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="12">
         <v>20</v>
       </c>
@@ -8107,6 +8141,9 @@
         <v>1</v>
       </c>
       <c r="J16" s="12">
+        <v>1</v>
+      </c>
+      <c r="K16" s="12">
         <v>1</v>
       </c>
       <c r="M16" s="12">
@@ -8145,8 +8182,12 @@
         <f t="shared" si="2"/>
         <v>2021</v>
       </c>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="17">
+        <f t="shared" si="2"/>
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B17" s="12">
         <v>20</v>
       </c>
@@ -8172,6 +8213,9 @@
         <v>1</v>
       </c>
       <c r="J17" s="12">
+        <v>1</v>
+      </c>
+      <c r="K17" s="12">
         <v>1</v>
       </c>
       <c r="M17" s="12">
@@ -8210,8 +8254,12 @@
         <f t="shared" si="2"/>
         <v>2022</v>
       </c>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="17">
+        <f t="shared" si="2"/>
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C18" s="12">
         <v>5</v>
       </c>
@@ -8236,6 +8284,9 @@
       <c r="J18" s="12">
         <v>1</v>
       </c>
+      <c r="K18" s="12">
+        <v>1</v>
+      </c>
       <c r="N18" s="12">
         <f t="shared" si="2"/>
         <v>2027</v>
@@ -8268,8 +8319,12 @@
         <f t="shared" si="2"/>
         <v>2023</v>
       </c>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="17">
+        <f t="shared" si="2"/>
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C19" s="12">
         <v>45</v>
       </c>
@@ -8294,6 +8349,9 @@
       <c r="J19" s="12">
         <v>1</v>
       </c>
+      <c r="K19" s="12">
+        <v>1</v>
+      </c>
       <c r="N19" s="12">
         <f t="shared" si="2"/>
         <v>2072</v>
@@ -8326,8 +8384,12 @@
         <f t="shared" si="2"/>
         <v>2024</v>
       </c>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="17">
+        <f t="shared" si="2"/>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C20" s="12">
         <v>25</v>
       </c>
@@ -8352,6 +8414,9 @@
       <c r="J20" s="12">
         <v>1</v>
       </c>
+      <c r="K20" s="12">
+        <v>1</v>
+      </c>
       <c r="N20" s="12">
         <f t="shared" si="2"/>
         <v>2097</v>
@@ -8384,8 +8449,12 @@
         <f t="shared" si="2"/>
         <v>2025</v>
       </c>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="17">
+        <f t="shared" si="2"/>
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C21" s="12">
         <v>5</v>
       </c>
@@ -8409,6 +8478,9 @@
       </c>
       <c r="J21" s="12">
         <v>10</v>
+      </c>
+      <c r="K21" s="12">
+        <v>3</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="2"/>
@@ -8442,8 +8514,12 @@
         <f>+U20+J21-5</f>
         <v>2030</v>
       </c>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="17">
+        <f>+V20+K21-1</f>
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
       <c r="D22" s="12">
         <v>5</v>
       </c>
@@ -8465,6 +8541,9 @@
       <c r="J22" s="12">
         <v>10</v>
       </c>
+      <c r="K22" s="12">
+        <v>4</v>
+      </c>
       <c r="O22" s="12">
         <f t="shared" si="2"/>
         <v>2062</v>
@@ -8493,8 +8572,12 @@
         <f t="shared" si="2"/>
         <v>2040</v>
       </c>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="17">
+        <f>+V21+K22-2</f>
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
       <c r="D23" s="12">
         <v>5</v>
       </c>
@@ -8516,6 +8599,9 @@
       <c r="J23" s="12">
         <v>10</v>
       </c>
+      <c r="K23" s="12">
+        <v>5</v>
+      </c>
       <c r="O23" s="12">
         <f t="shared" si="2"/>
         <v>2067</v>
@@ -8544,8 +8630,12 @@
         <f t="shared" si="2"/>
         <v>2050</v>
       </c>
-    </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="17">
+        <f t="shared" si="2"/>
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
       <c r="D24" s="12">
         <v>5</v>
       </c>
@@ -8567,6 +8657,9 @@
       <c r="J24" s="12">
         <v>10</v>
       </c>
+      <c r="K24" s="12">
+        <v>5</v>
+      </c>
       <c r="O24" s="12">
         <f t="shared" si="2"/>
         <v>2072</v>
@@ -8595,8 +8688,12 @@
         <f t="shared" si="2"/>
         <v>2060</v>
       </c>
-    </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="17">
+        <f t="shared" si="2"/>
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="E25" s="12">
         <v>5</v>
       </c>
@@ -8615,6 +8712,9 @@
       <c r="J25" s="12">
         <v>10</v>
       </c>
+      <c r="K25" s="12">
+        <v>5</v>
+      </c>
       <c r="P25" s="12">
         <f t="shared" si="2"/>
         <v>2072</v>
@@ -8639,8 +8739,12 @@
         <f t="shared" si="2"/>
         <v>2070</v>
       </c>
-    </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="17">
+        <f t="shared" si="2"/>
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="F26" s="12">
         <v>5</v>
       </c>
@@ -8656,6 +8760,9 @@
       <c r="J26" s="12">
         <v>10</v>
       </c>
+      <c r="K26" s="12">
+        <v>5</v>
+      </c>
       <c r="Q26" s="12">
         <f t="shared" si="2"/>
         <v>2067</v>
@@ -8676,8 +8783,12 @@
         <f t="shared" si="2"/>
         <v>2080</v>
       </c>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="17">
+        <f t="shared" si="2"/>
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="F27" s="12">
         <v>5</v>
       </c>
@@ -8693,6 +8804,9 @@
       <c r="J27" s="12">
         <v>10</v>
       </c>
+      <c r="K27" s="12">
+        <v>5</v>
+      </c>
       <c r="Q27" s="12">
         <f t="shared" si="2"/>
         <v>2072</v>
@@ -8713,8 +8827,12 @@
         <f t="shared" si="2"/>
         <v>2090</v>
       </c>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="17">
+        <f t="shared" si="2"/>
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="G28" s="12">
         <v>5</v>
       </c>
@@ -8727,6 +8845,9 @@
       <c r="J28" s="12">
         <v>10</v>
       </c>
+      <c r="K28" s="12">
+        <v>5</v>
+      </c>
       <c r="R28" s="12">
         <f t="shared" si="2"/>
         <v>2037</v>
@@ -8743,8 +8864,12 @@
         <f t="shared" si="2"/>
         <v>2100</v>
       </c>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="17">
+        <f t="shared" si="2"/>
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="G29" s="12">
         <v>5</v>
       </c>
@@ -8754,6 +8879,9 @@
       <c r="I29" s="17">
         <v>1</v>
       </c>
+      <c r="K29" s="12">
+        <v>5</v>
+      </c>
       <c r="R29" s="12">
         <f t="shared" si="2"/>
         <v>2042</v>
@@ -8766,8 +8894,12 @@
         <f t="shared" si="2"/>
         <v>2034</v>
       </c>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="17">
+        <f t="shared" si="2"/>
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="G30" s="12">
         <v>5</v>
       </c>
@@ -8776,6 +8908,9 @@
       </c>
       <c r="I30" s="17">
         <v>1</v>
+      </c>
+      <c r="K30" s="12">
+        <v>5</v>
       </c>
       <c r="R30" s="12">
         <f t="shared" ref="R30:T45" si="4">+R29+G30</f>
@@ -8789,8 +8924,12 @@
         <f t="shared" si="4"/>
         <v>2035</v>
       </c>
-    </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="17">
+        <f t="shared" ref="V30:V35" si="5">+V29+K30</f>
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
       <c r="G31" s="12">
         <v>5</v>
       </c>
@@ -8799,6 +8938,9 @@
       </c>
       <c r="I31" s="17">
         <v>1</v>
+      </c>
+      <c r="K31" s="12">
+        <v>5</v>
       </c>
       <c r="R31" s="12">
         <f t="shared" si="4"/>
@@ -8812,8 +8954,12 @@
         <f t="shared" si="4"/>
         <v>2036</v>
       </c>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="17">
+        <f t="shared" si="5"/>
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
       <c r="G32" s="12">
         <v>5</v>
       </c>
@@ -8822,6 +8968,9 @@
       </c>
       <c r="I32" s="17">
         <v>1</v>
+      </c>
+      <c r="K32" s="12">
+        <v>5</v>
       </c>
       <c r="R32" s="12">
         <f t="shared" si="4"/>
@@ -8835,8 +8984,12 @@
         <f t="shared" si="4"/>
         <v>2037</v>
       </c>
-    </row>
-    <row r="33" spans="7:20" x14ac:dyDescent="0.2">
+      <c r="V32" s="17">
+        <f t="shared" si="5"/>
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="33" spans="7:22" x14ac:dyDescent="0.25">
       <c r="G33" s="12">
         <v>5</v>
       </c>
@@ -8845,6 +8998,9 @@
       </c>
       <c r="I33" s="17">
         <v>1</v>
+      </c>
+      <c r="K33" s="12">
+        <v>5</v>
       </c>
       <c r="R33" s="12">
         <f t="shared" si="4"/>
@@ -8858,8 +9014,12 @@
         <f t="shared" si="4"/>
         <v>2038</v>
       </c>
-    </row>
-    <row r="34" spans="7:20" x14ac:dyDescent="0.2">
+      <c r="V33" s="17">
+        <f t="shared" si="5"/>
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="34" spans="7:22" x14ac:dyDescent="0.25">
       <c r="G34" s="12">
         <v>5</v>
       </c>
@@ -8868,6 +9028,9 @@
       </c>
       <c r="I34" s="17">
         <v>1</v>
+      </c>
+      <c r="K34" s="12">
+        <v>5</v>
       </c>
       <c r="R34" s="12">
         <f t="shared" si="4"/>
@@ -8881,8 +9044,12 @@
         <f t="shared" si="4"/>
         <v>2039</v>
       </c>
-    </row>
-    <row r="35" spans="7:20" x14ac:dyDescent="0.2">
+      <c r="V34" s="17">
+        <f t="shared" si="5"/>
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="35" spans="7:22" x14ac:dyDescent="0.25">
       <c r="G35" s="12">
         <v>5</v>
       </c>
@@ -8891,6 +9058,9 @@
       </c>
       <c r="I35" s="17">
         <v>1</v>
+      </c>
+      <c r="K35" s="12">
+        <v>5</v>
       </c>
       <c r="R35" s="12">
         <f t="shared" si="4"/>
@@ -8904,13 +9074,20 @@
         <f t="shared" si="4"/>
         <v>2040</v>
       </c>
-    </row>
-    <row r="36" spans="7:20" x14ac:dyDescent="0.2">
+      <c r="V35" s="17">
+        <f t="shared" si="5"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="36" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H36" s="17">
         <v>1</v>
       </c>
       <c r="I36" s="17">
         <v>1</v>
+      </c>
+      <c r="K36" s="12">
+        <v>5</v>
       </c>
       <c r="S36" s="17">
         <f t="shared" si="4"/>
@@ -8920,8 +9097,12 @@
         <f t="shared" si="4"/>
         <v>2041</v>
       </c>
-    </row>
-    <row r="37" spans="7:20" x14ac:dyDescent="0.2">
+      <c r="V36" s="17">
+        <f>+V35+K36</f>
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="37" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H37" s="17">
         <v>1</v>
       </c>
@@ -8937,7 +9118,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="38" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H38" s="17">
         <v>1</v>
       </c>
@@ -8953,7 +9134,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="39" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H39" s="17">
         <v>1</v>
       </c>
@@ -8969,7 +9150,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="40" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="40" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H40" s="17">
         <v>1</v>
       </c>
@@ -8985,7 +9166,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="41" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="41" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H41" s="17">
         <v>1</v>
       </c>
@@ -9001,7 +9182,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="42" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H42" s="17">
         <v>1</v>
       </c>
@@ -9017,7 +9198,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="43" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H43" s="17">
         <v>1</v>
       </c>
@@ -9033,7 +9214,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="44" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H44" s="17">
         <v>1</v>
       </c>
@@ -9049,7 +9230,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="45" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H45" s="17">
         <v>1</v>
       </c>
@@ -9065,7 +9246,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="46" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="7:22" x14ac:dyDescent="0.25">
       <c r="I46" s="17">
         <v>1</v>
       </c>
@@ -9074,7 +9255,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="47" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="7:22" x14ac:dyDescent="0.25">
       <c r="I47" s="17">
         <v>1</v>
       </c>
@@ -9083,7 +9264,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="48" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="7:22" x14ac:dyDescent="0.25">
       <c r="I48" s="17">
         <v>5</v>
       </c>
@@ -9092,34 +9273,35 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="49" spans="9:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I49" s="17">
         <v>5</v>
       </c>
       <c r="T49" s="17">
-        <f t="shared" ref="T49:T51" si="5">+T48+I49</f>
+        <f t="shared" ref="T49:T51" si="6">+T48+I49</f>
         <v>2060</v>
       </c>
     </row>
-    <row r="50" spans="9:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I50" s="17">
         <v>5</v>
       </c>
       <c r="T50" s="17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2065</v>
       </c>
     </row>
-    <row r="51" spans="9:20" x14ac:dyDescent="0.2">
+    <row r="51" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I51" s="17">
         <v>5</v>
       </c>
       <c r="T51" s="17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2070</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -9130,17 +9312,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B3:C9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="52.7109375" customWidth="1"/>
+    <col min="2" max="2" width="52.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
         <v>25</v>
       </c>
@@ -9148,7 +9330,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="17" t="s">
         <v>27</v>
       </c>
@@ -9156,7 +9338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>28</v>
       </c>
@@ -9164,7 +9346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
         <v>29</v>
       </c>
@@ -9172,7 +9354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="12" t="s">
         <v>30</v>
       </c>
@@ -9180,7 +9362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>49</v>
       </c>
@@ -9199,42 +9381,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:P24"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" customWidth="1"/>
-    <col min="8" max="8" width="6.28515625" customWidth="1"/>
-    <col min="12" max="12" width="9.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="6.44140625" customWidth="1"/>
+    <col min="8" max="8" width="6.33203125" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="O3" s="24"/>
       <c r="P3" s="24"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="O4" s="24"/>
       <c r="P4" s="24"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="O7" s="24"/>
       <c r="P7" s="24"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="24"/>
       <c r="B8" s="24"/>
       <c r="C8" s="24"/>
@@ -9252,7 +9434,7 @@
       <c r="O8" s="24"/>
       <c r="P8" s="24"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
@@ -9270,7 +9452,7 @@
       <c r="O9" s="24"/>
       <c r="P9" s="24"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="24"/>
       <c r="B10" s="24"/>
       <c r="C10" s="24"/>
@@ -9288,7 +9470,7 @@
       <c r="O10" s="24"/>
       <c r="P10" s="24"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="24"/>
       <c r="B11" s="24"/>
       <c r="C11" s="24"/>
@@ -9306,7 +9488,7 @@
       <c r="O11" s="24"/>
       <c r="P11" s="24"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="24"/>
       <c r="B12" s="24"/>
       <c r="C12" s="24"/>
@@ -9324,7 +9506,7 @@
       <c r="O12" s="24"/>
       <c r="P12" s="24"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="18" t="s">
         <v>52</v>
       </c>
@@ -9343,7 +9525,7 @@
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>0</v>
       </c>
@@ -9363,7 +9545,7 @@
       <c r="O14" s="24"/>
       <c r="P14" s="24"/>
     </row>
-    <row r="15" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>12</v>
       </c>
@@ -9413,7 +9595,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="24"/>
       <c r="B16" s="24"/>
       <c r="C16" s="24" t="s">
@@ -9439,7 +9621,7 @@
       <c r="O16" s="24"/>
       <c r="P16" s="24"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="24"/>
       <c r="B17" s="24"/>
       <c r="C17" s="24" t="s">
@@ -9465,7 +9647,7 @@
       <c r="O17" s="24"/>
       <c r="P17" s="24"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="24"/>
       <c r="B18" s="24"/>
       <c r="C18" s="24"/>
@@ -9483,7 +9665,7 @@
       <c r="O18" s="24"/>
       <c r="P18" s="24"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>11</v>
       </c>
@@ -9503,7 +9685,7 @@
       <c r="O19" s="24"/>
       <c r="P19" s="24"/>
     </row>
-    <row r="20" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
         <v>12</v>
       </c>
@@ -9553,7 +9735,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
         <v>165</v>
       </c>
@@ -9587,7 +9769,7 @@
       </c>
       <c r="P21" s="24"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="24"/>
       <c r="B22" s="24"/>
       <c r="C22" s="24" t="s">
@@ -9611,7 +9793,7 @@
       <c r="O22" s="24"/>
       <c r="P22" s="24"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="24"/>
       <c r="B23" s="24"/>
       <c r="C23" s="24"/>
@@ -9629,7 +9811,7 @@
       <c r="O23" s="24"/>
       <c r="P23" s="24"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="24"/>
       <c r="B24" s="24"/>
       <c r="C24" s="24"/>
@@ -9658,27 +9840,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B1:G34"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="22" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
@@ -9698,7 +9880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="D5" s="7" t="s">
         <v>39</v>
       </c>
@@ -9706,7 +9888,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B6" s="26"/>
       <c r="C6" s="26"/>
       <c r="D6" s="26" t="s">
@@ -9718,7 +9900,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B7" s="26"/>
       <c r="C7" s="26" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B3,4))</f>
@@ -9736,7 +9918,7 @@
         <v>1.3926669328933141</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7"/>
       <c r="C8" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B4,4))</f>
@@ -9754,7 +9936,7 @@
         <v>1.3626878012654737</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B9" s="7"/>
       <c r="C9" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B5,4))</f>
@@ -9772,7 +9954,7 @@
         <v>1.3346599424735295</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B10" s="7"/>
       <c r="C10" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B6,4))</f>
@@ -9790,7 +9972,7 @@
         <v>1.3084901396799309</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B11" s="7"/>
       <c r="C11" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B7,4))</f>
@@ -9808,7 +9990,7 @@
         <v>1.2828334702744419</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B12" s="7"/>
       <c r="C12" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B8,4))</f>
@@ -9826,7 +10008,7 @@
         <v>1.2552186597597279</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B13" s="7"/>
       <c r="C13" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B9,4))</f>
@@ -9844,7 +10026,7 @@
         <v>1.2281982972208687</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B14" s="7"/>
       <c r="C14" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B10,4))</f>
@@ -9862,7 +10044,7 @@
         <v>1.2005848457682002</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B11,4))</f>
@@ -9880,7 +10062,7 @@
         <v>1.1577481637108971</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B16" s="7"/>
       <c r="C16" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B12,4))</f>
@@ -9898,7 +10080,7 @@
         <v>1.1462853106048485</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B17" s="7"/>
       <c r="C17" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B13,4))</f>
@@ -9916,7 +10098,7 @@
         <v>1.1227084335013209</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B18" s="7"/>
       <c r="C18" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B14,4))</f>
@@ -9934,7 +10116,7 @@
         <v>1.0889509539295061</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B19" s="7"/>
       <c r="C19" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B15,4))</f>
@@ -9952,7 +10134,7 @@
         <v>1.0613557055843141</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B20" s="7"/>
       <c r="C20" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B16,4))</f>
@@ -9970,7 +10152,7 @@
         <v>1.045670645895876</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B17,4))</f>
@@ -9988,7 +10170,7 @@
         <v>1.0394340416460002</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B22" s="7"/>
       <c r="C22" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B18,4))</f>
@@ -10006,7 +10188,7 @@
         <v>1.0383956459999999</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
       <c r="C23" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B19,4))</f>
@@ -10024,7 +10206,7 @@
         <v>1.0363230000000001</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
       <c r="C24" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B20,4))</f>
@@ -10042,7 +10224,7 @@
         <v>1.0190000000000001</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B25" s="7"/>
       <c r="C25" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B22,4))</f>
@@ -10060,7 +10242,7 @@
         <v>0.98522167487684731</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="C26" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B23,4))</f>
         <v>MEUR2020</v>
@@ -10077,7 +10259,7 @@
         <v>0.9783730634328176</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="C27" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B24,4))</f>
         <v>MEUR2021</v>
@@ -10094,16 +10276,16 @@
         <v>0.95079986728164989</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B31" s="7"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B32" s="7"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B33" s="7"/>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B34" s="25"/>
     </row>
   </sheetData>
@@ -10117,12 +10299,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:O25"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B2" s="10" t="s">
         <v>43</v>
       </c>
@@ -10133,7 +10315,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="2:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="9" t="s">
         <v>44</v>
       </c>
@@ -10171,7 +10353,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>161</v>
       </c>
@@ -10200,7 +10382,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="str">
         <f>Constants!C7</f>
         <v>MEUR2000</v>
@@ -10230,7 +10412,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="str">
         <f>Constants!C8</f>
         <v>MEUR2001</v>
@@ -10260,7 +10442,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="str">
         <f>Constants!C9</f>
         <v>MEUR2002</v>
@@ -10275,7 +10457,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="str">
         <f>Constants!C10</f>
         <v>MEUR2003</v>
@@ -10290,7 +10472,7 @@
         <v>41.87</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="str">
         <f>Constants!C11</f>
         <v>MEUR2004</v>
@@ -10305,7 +10487,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="str">
         <f>Constants!C12</f>
         <v>MEUR2005</v>
@@ -10320,7 +10502,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="str">
         <f>Constants!C13</f>
         <v>MEUR2006</v>
@@ -10335,7 +10517,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="str">
         <f>Constants!C14</f>
         <v>MEUR2007</v>
@@ -10350,7 +10532,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="str">
         <f>Constants!C15</f>
         <v>MEUR2008</v>
@@ -10365,7 +10547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="str">
         <f>Constants!C16</f>
         <v>MEUR2009</v>
@@ -10380,7 +10562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="str">
         <f>Constants!C17</f>
         <v>MEUR2010</v>
@@ -10395,61 +10577,61 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="str">
         <f>Constants!C18</f>
         <v>MEUR2011</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="str">
         <f>Constants!C19</f>
         <v>MEUR2012</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="str">
         <f>Constants!C20</f>
         <v>MEUR2013</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="str">
         <f>Constants!C21</f>
         <v>MEUR2014</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="str">
         <f>Constants!C22</f>
         <v>MEUR2015</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="str">
         <f>Constants!C23</f>
         <v>MEUR2016</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="str">
         <f>Constants!C24</f>
         <v>MEUR2017</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="str">
         <f>Constants!C25</f>
         <v>MEUR2019</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="str">
         <f>Constants!C26</f>
         <v>MEUR2020</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="str">
         <f>Constants!C27</f>
         <v>MEUR2021</v>
@@ -10466,13 +10648,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:D26"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="4" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="4" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="28"/>
       <c r="C2" s="29" t="s">
         <v>34</v>
@@ -10481,7 +10663,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B3" s="31">
         <v>2000</v>
       </c>
@@ -10490,7 +10672,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B4" s="31">
         <v>2001</v>
       </c>
@@ -10502,7 +10684,7 @@
         <v>102.2</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B5" s="31">
         <v>2002</v>
       </c>
@@ -10514,7 +10696,7 @@
         <v>104.34620000000001</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B6" s="31">
         <v>2003</v>
       </c>
@@ -10526,7 +10708,7 @@
         <v>106.43312400000001</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B7" s="31">
         <v>2004</v>
       </c>
@@ -10538,7 +10720,7 @@
         <v>108.56178648000001</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B8" s="31">
         <v>2005</v>
       </c>
@@ -10550,7 +10732,7 @@
         <v>110.95014578256001</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B9" s="31">
         <v>2006</v>
       </c>
@@ -10562,7 +10744,7 @@
         <v>113.39104898977634</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B10" s="31">
         <v>2007</v>
       </c>
@@ -10574,7 +10756,7 @@
         <v>115.99904311654119</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B11" s="31">
         <v>2008</v>
       </c>
@@ -10586,7 +10768,7 @@
         <v>120.29100771185321</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B12" s="31">
         <v>2009</v>
       </c>
@@ -10598,7 +10780,7 @@
         <v>121.49391778897174</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B13" s="31">
         <v>2010</v>
       </c>
@@ -10610,7 +10792,7 @@
         <v>124.04529006254015</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B14" s="31">
         <v>2011</v>
       </c>
@@ -10622,7 +10804,7 @@
         <v>127.89069405447889</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B15" s="31">
         <v>2012</v>
       </c>
@@ -10634,7 +10816,7 @@
         <v>131.21585209989533</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B16" s="31">
         <v>2013</v>
       </c>
@@ -10646,7 +10828,7 @@
         <v>133.18408988139376</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B17" s="31">
         <v>2014</v>
       </c>
@@ -10658,7 +10840,7 @@
         <v>133.98319442068211</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B18" s="31">
         <v>2015</v>
       </c>
@@ -10670,7 +10852,7 @@
         <v>134.1171776151028</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B19" s="36">
         <v>2016</v>
       </c>
@@ -10682,7 +10864,7 @@
         <v>134.385411970333</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B20" s="36">
         <v>2017</v>
       </c>
@@ -10694,7 +10876,7 @@
         <v>136.66996397382866</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B21" s="36">
         <v>2018</v>
       </c>
@@ -10706,7 +10888,7 @@
         <v>139.26669328933141</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B22" s="36">
         <v>2019</v>
       </c>
@@ -10718,7 +10900,7 @@
         <v>141.35569368867138</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B23" s="36">
         <v>2020</v>
       </c>
@@ -10730,7 +10912,7 @@
         <v>142.34518354449207</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B24" s="36">
         <v>2021</v>
       </c>
@@ -10742,7 +10924,7 @@
         <v>146.47319386728233</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B26" s="35" t="s">
         <v>36</v>
       </c>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC284C4A-2A9D-4CEB-9206-1C51106AA5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BB1EBD-AD17-47CD-994B-6C52298E6487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="28" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="170">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -1563,7 +1563,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>30480</xdr:colOff>
+          <xdr:colOff>31750</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -4012,21 +4012,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3D08AF-561B-4741-93FB-876D250B4223}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="21.6640625" style="42" customWidth="1"/>
-    <col min="5" max="6" width="14.109375" style="42" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="42" customWidth="1"/>
-    <col min="8" max="10" width="8.109375" style="42" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="42" customWidth="1"/>
-    <col min="12" max="12" width="8.109375" style="42" customWidth="1"/>
+    <col min="1" max="4" width="21.6328125" style="42" customWidth="1"/>
+    <col min="5" max="6" width="14.08984375" style="42" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" style="42" customWidth="1"/>
+    <col min="8" max="10" width="8.08984375" style="42" customWidth="1"/>
+    <col min="11" max="11" width="9.6328125" style="42" customWidth="1"/>
+    <col min="12" max="12" width="8.08984375" style="42" customWidth="1"/>
     <col min="13" max="13" width="10" style="42" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="42" customWidth="1"/>
-    <col min="15" max="15" width="13.44140625" style="42" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="42"/>
+    <col min="14" max="14" width="11.453125" style="42" customWidth="1"/>
+    <col min="15" max="15" width="13.453125" style="42" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" s="40"/>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -4054,7 +4054,7 @@
       <c r="Y1" s="41"/>
       <c r="Z1" s="41"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -4082,7 +4082,7 @@
       <c r="Y2" s="41"/>
       <c r="Z2" s="41"/>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="40"/>
       <c r="B3" s="40"/>
       <c r="C3" s="40"/>
@@ -4110,7 +4110,7 @@
       <c r="Y3" s="41"/>
       <c r="Z3" s="41"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="40"/>
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
@@ -4138,7 +4138,7 @@
       <c r="Y4" s="41"/>
       <c r="Z4" s="41"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="40"/>
       <c r="B5" s="40"/>
       <c r="C5" s="40"/>
@@ -4166,7 +4166,7 @@
       <c r="Y5" s="41"/>
       <c r="Z5" s="41"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="40"/>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
@@ -4194,7 +4194,7 @@
       <c r="Y6" s="41"/>
       <c r="Z6" s="41"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="40"/>
       <c r="B7" s="40"/>
       <c r="C7" s="40"/>
@@ -4222,7 +4222,7 @@
       <c r="Y7" s="41"/>
       <c r="Z7" s="41"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="40"/>
       <c r="B8" s="40"/>
       <c r="C8" s="40"/>
@@ -4250,7 +4250,7 @@
       <c r="Y8" s="41"/>
       <c r="Z8" s="41"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="40"/>
       <c r="B9" s="40"/>
       <c r="C9" s="40"/>
@@ -4278,7 +4278,7 @@
       <c r="Y9" s="41"/>
       <c r="Z9" s="41"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="40"/>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
@@ -4306,7 +4306,7 @@
       <c r="Y10" s="41"/>
       <c r="Z10" s="41"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="40"/>
       <c r="B11" s="40"/>
       <c r="C11" s="40"/>
@@ -4334,7 +4334,7 @@
       <c r="Y11" s="41"/>
       <c r="Z11" s="41"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="40"/>
       <c r="B12" s="40"/>
       <c r="C12" s="40"/>
@@ -4362,7 +4362,7 @@
       <c r="Y12" s="41"/>
       <c r="Z12" s="41"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="40"/>
       <c r="B13" s="40"/>
       <c r="C13" s="40"/>
@@ -4390,7 +4390,7 @@
       <c r="Y13" s="41"/>
       <c r="Z13" s="41"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="40"/>
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
@@ -4418,7 +4418,7 @@
       <c r="Y14" s="41"/>
       <c r="Z14" s="41"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="40"/>
       <c r="B15" s="40"/>
       <c r="C15" s="40"/>
@@ -4446,7 +4446,7 @@
       <c r="Y15" s="41"/>
       <c r="Z15" s="41"/>
     </row>
-    <row r="16" spans="1:26" ht="102.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="102.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="57" t="s">
         <v>144</v>
       </c>
@@ -4476,7 +4476,7 @@
       <c r="Y16" s="41"/>
       <c r="Z16" s="41"/>
     </row>
-    <row r="17" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="45"/>
       <c r="B17" s="45"/>
       <c r="C17" s="45"/>
@@ -4504,7 +4504,7 @@
       <c r="Y17" s="41"/>
       <c r="Z17" s="41"/>
     </row>
-    <row r="18" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="45"/>
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
@@ -4532,7 +4532,7 @@
       <c r="Y18" s="41"/>
       <c r="Z18" s="41"/>
     </row>
-    <row r="19" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="48" t="s">
         <v>145</v>
       </c>
@@ -4564,7 +4564,7 @@
       <c r="Y19" s="41"/>
       <c r="Z19" s="41"/>
     </row>
-    <row r="20" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="48" t="s">
         <v>146</v>
       </c>
@@ -4596,7 +4596,7 @@
       <c r="Y20" s="41"/>
       <c r="Z20" s="41"/>
     </row>
-    <row r="21" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="48" t="s">
         <v>147</v>
       </c>
@@ -4628,7 +4628,7 @@
       <c r="Y21" s="41"/>
       <c r="Z21" s="41"/>
     </row>
-    <row r="22" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="48"/>
       <c r="B22" s="51"/>
       <c r="C22" s="51"/>
@@ -4656,7 +4656,7 @@
       <c r="Y22" s="41"/>
       <c r="Z22" s="41"/>
     </row>
-    <row r="23" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="48" t="s">
         <v>148</v>
       </c>
@@ -4688,7 +4688,7 @@
       <c r="Y23" s="41"/>
       <c r="Z23" s="41"/>
     </row>
-    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="48"/>
       <c r="B24" s="51" t="s">
         <v>159</v>
@@ -4718,7 +4718,7 @@
       <c r="Y24" s="41"/>
       <c r="Z24" s="41"/>
     </row>
-    <row r="25" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="48"/>
       <c r="B25" s="51"/>
       <c r="C25" s="51"/>
@@ -4746,7 +4746,7 @@
       <c r="Y25" s="41"/>
       <c r="Z25" s="41"/>
     </row>
-    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="48" t="s">
         <v>149</v>
       </c>
@@ -4778,7 +4778,7 @@
       <c r="Y26" s="41"/>
       <c r="Z26" s="41"/>
     </row>
-    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="48"/>
       <c r="B27" s="51"/>
       <c r="C27" s="51"/>
@@ -4806,7 +4806,7 @@
       <c r="Y27" s="41"/>
       <c r="Z27" s="41"/>
     </row>
-    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="48"/>
       <c r="B28" s="51"/>
       <c r="C28" s="51"/>
@@ -4834,7 +4834,7 @@
       <c r="Y28" s="41"/>
       <c r="Z28" s="41"/>
     </row>
-    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="48" t="s">
         <v>150</v>
       </c>
@@ -4866,7 +4866,7 @@
       <c r="Y29" s="41"/>
       <c r="Z29" s="41"/>
     </row>
-    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="48" t="s">
         <v>151</v>
       </c>
@@ -4898,7 +4898,7 @@
       <c r="Y30" s="41"/>
       <c r="Z30" s="41"/>
     </row>
-    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="48" t="s">
         <v>153</v>
       </c>
@@ -4930,7 +4930,7 @@
       <c r="Y31" s="41"/>
       <c r="Z31" s="41"/>
     </row>
-    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="54"/>
       <c r="B32" s="55" t="s">
         <v>155</v>
@@ -4960,7 +4960,7 @@
       <c r="Y32" s="41"/>
       <c r="Z32" s="41"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A33" s="40"/>
       <c r="B33" s="40"/>
       <c r="C33" s="40"/>
@@ -4988,7 +4988,7 @@
       <c r="Y33" s="41"/>
       <c r="Z33" s="41"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A34" s="40"/>
       <c r="B34" s="40"/>
       <c r="C34" s="40"/>
@@ -5016,7 +5016,7 @@
       <c r="Y34" s="41"/>
       <c r="Z34" s="41"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A35" s="40"/>
       <c r="B35" s="40"/>
       <c r="C35" s="40"/>
@@ -5044,7 +5044,7 @@
       <c r="Y35" s="41"/>
       <c r="Z35" s="41"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A36" s="40"/>
       <c r="B36" s="40"/>
       <c r="C36" s="40"/>
@@ -5072,7 +5072,7 @@
       <c r="Y36" s="41"/>
       <c r="Z36" s="41"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A37" s="40"/>
       <c r="B37" s="40"/>
       <c r="C37" s="40"/>
@@ -5100,7 +5100,7 @@
       <c r="Y37" s="41"/>
       <c r="Z37" s="41"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A38" s="40"/>
       <c r="B38" s="40"/>
       <c r="C38" s="40"/>
@@ -5128,7 +5128,7 @@
       <c r="Y38" s="41"/>
       <c r="Z38" s="41"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A39" s="40"/>
       <c r="B39" s="40"/>
       <c r="C39" s="40"/>
@@ -5156,7 +5156,7 @@
       <c r="Y39" s="41"/>
       <c r="Z39" s="41"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A40" s="40"/>
       <c r="B40" s="40"/>
       <c r="C40" s="40"/>
@@ -5184,7 +5184,7 @@
       <c r="Y40" s="41"/>
       <c r="Z40" s="41"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A41" s="40"/>
       <c r="B41" s="40"/>
       <c r="C41" s="40"/>
@@ -5212,7 +5212,7 @@
       <c r="Y41" s="41"/>
       <c r="Z41" s="41"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A42" s="40"/>
       <c r="B42" s="40"/>
       <c r="C42" s="40"/>
@@ -5240,7 +5240,7 @@
       <c r="Y42" s="41"/>
       <c r="Z42" s="41"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A43" s="41"/>
       <c r="B43" s="41"/>
       <c r="C43" s="41"/>
@@ -5268,7 +5268,7 @@
       <c r="Y43" s="41"/>
       <c r="Z43" s="41"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A44" s="41"/>
       <c r="B44" s="41"/>
       <c r="C44" s="41"/>
@@ -5296,7 +5296,7 @@
       <c r="Y44" s="41"/>
       <c r="Z44" s="41"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A45" s="41"/>
       <c r="B45" s="41"/>
       <c r="C45" s="41"/>
@@ -5324,7 +5324,7 @@
       <c r="Y45" s="41"/>
       <c r="Z45" s="41"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A46" s="41"/>
       <c r="B46" s="41"/>
       <c r="C46" s="41"/>
@@ -5352,7 +5352,7 @@
       <c r="Y46" s="41"/>
       <c r="Z46" s="41"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A47" s="41"/>
       <c r="B47" s="41"/>
       <c r="C47" s="41"/>
@@ -5380,7 +5380,7 @@
       <c r="Y47" s="41"/>
       <c r="Z47" s="41"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A48" s="41"/>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
@@ -5408,7 +5408,7 @@
       <c r="Y48" s="41"/>
       <c r="Z48" s="41"/>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A49" s="41"/>
       <c r="B49" s="41"/>
       <c r="C49" s="41"/>
@@ -5436,7 +5436,7 @@
       <c r="Y49" s="41"/>
       <c r="Z49" s="41"/>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A50" s="41"/>
       <c r="B50" s="41"/>
       <c r="C50" s="41"/>
@@ -5464,7 +5464,7 @@
       <c r="Y50" s="41"/>
       <c r="Z50" s="41"/>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A51" s="41"/>
       <c r="B51" s="41"/>
       <c r="C51" s="41"/>
@@ -5492,7 +5492,7 @@
       <c r="Y51" s="41"/>
       <c r="Z51" s="41"/>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A52" s="41"/>
       <c r="B52" s="41"/>
       <c r="C52" s="41"/>
@@ -5520,7 +5520,7 @@
       <c r="Y52" s="41"/>
       <c r="Z52" s="41"/>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A53" s="41"/>
       <c r="B53" s="41"/>
       <c r="C53" s="41"/>
@@ -5548,7 +5548,7 @@
       <c r="Y53" s="41"/>
       <c r="Z53" s="41"/>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A54" s="41"/>
       <c r="B54" s="41"/>
       <c r="C54" s="41"/>
@@ -5576,7 +5576,7 @@
       <c r="Y54" s="41"/>
       <c r="Z54" s="41"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A55" s="41"/>
       <c r="B55" s="41"/>
       <c r="C55" s="41"/>
@@ -5604,7 +5604,7 @@
       <c r="Y55" s="41"/>
       <c r="Z55" s="41"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A56" s="41"/>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -5632,7 +5632,7 @@
       <c r="Y56" s="41"/>
       <c r="Z56" s="41"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A57" s="41"/>
       <c r="B57" s="41"/>
       <c r="C57" s="41"/>
@@ -5660,7 +5660,7 @@
       <c r="Y57" s="41"/>
       <c r="Z57" s="41"/>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A58" s="41"/>
       <c r="B58" s="41"/>
       <c r="C58" s="41"/>
@@ -5688,7 +5688,7 @@
       <c r="Y58" s="41"/>
       <c r="Z58" s="41"/>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A59" s="41"/>
       <c r="B59" s="41"/>
       <c r="C59" s="41"/>
@@ -5716,7 +5716,7 @@
       <c r="Y59" s="41"/>
       <c r="Z59" s="41"/>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A60" s="41"/>
       <c r="B60" s="41"/>
       <c r="C60" s="41"/>
@@ -5744,7 +5744,7 @@
       <c r="Y60" s="41"/>
       <c r="Z60" s="41"/>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A61" s="41"/>
       <c r="B61" s="41"/>
       <c r="C61" s="41"/>
@@ -5772,7 +5772,7 @@
       <c r="Y61" s="41"/>
       <c r="Z61" s="41"/>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A62" s="41"/>
       <c r="B62" s="41"/>
       <c r="C62" s="41"/>
@@ -5800,7 +5800,7 @@
       <c r="Y62" s="41"/>
       <c r="Z62" s="41"/>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A63" s="41"/>
       <c r="B63" s="41"/>
       <c r="C63" s="41"/>
@@ -5828,7 +5828,7 @@
       <c r="Y63" s="41"/>
       <c r="Z63" s="41"/>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A64" s="41"/>
       <c r="B64" s="41"/>
       <c r="C64" s="41"/>
@@ -5856,7 +5856,7 @@
       <c r="Y64" s="41"/>
       <c r="Z64" s="41"/>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A65" s="41"/>
       <c r="B65" s="41"/>
       <c r="C65" s="41"/>
@@ -5884,7 +5884,7 @@
       <c r="Y65" s="41"/>
       <c r="Z65" s="41"/>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A66" s="41"/>
       <c r="B66" s="41"/>
       <c r="C66" s="41"/>
@@ -5912,7 +5912,7 @@
       <c r="Y66" s="41"/>
       <c r="Z66" s="41"/>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A67" s="41"/>
       <c r="B67" s="41"/>
       <c r="C67" s="41"/>
@@ -5940,7 +5940,7 @@
       <c r="Y67" s="41"/>
       <c r="Z67" s="41"/>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A68" s="41"/>
       <c r="B68" s="41"/>
       <c r="C68" s="41"/>
@@ -5968,7 +5968,7 @@
       <c r="Y68" s="41"/>
       <c r="Z68" s="41"/>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A69" s="41"/>
       <c r="B69" s="41"/>
       <c r="C69" s="41"/>
@@ -5996,7 +5996,7 @@
       <c r="Y69" s="41"/>
       <c r="Z69" s="41"/>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A70" s="41"/>
       <c r="B70" s="41"/>
       <c r="C70" s="41"/>
@@ -6024,7 +6024,7 @@
       <c r="Y70" s="41"/>
       <c r="Z70" s="41"/>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A71" s="41"/>
       <c r="B71" s="41"/>
       <c r="C71" s="41"/>
@@ -6052,7 +6052,7 @@
       <c r="Y71" s="41"/>
       <c r="Z71" s="41"/>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A72" s="41"/>
       <c r="B72" s="41"/>
       <c r="C72" s="41"/>
@@ -6080,7 +6080,7 @@
       <c r="Y72" s="41"/>
       <c r="Z72" s="41"/>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A73" s="41"/>
       <c r="B73" s="41"/>
       <c r="C73" s="41"/>
@@ -6108,7 +6108,7 @@
       <c r="Y73" s="41"/>
       <c r="Z73" s="41"/>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A74" s="41"/>
       <c r="B74" s="41"/>
       <c r="C74" s="41"/>
@@ -6136,7 +6136,7 @@
       <c r="Y74" s="41"/>
       <c r="Z74" s="41"/>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A75" s="41"/>
       <c r="B75" s="41"/>
       <c r="C75" s="41"/>
@@ -6164,7 +6164,7 @@
       <c r="Y75" s="41"/>
       <c r="Z75" s="41"/>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A76" s="41"/>
       <c r="B76" s="41"/>
       <c r="C76" s="41"/>
@@ -6192,7 +6192,7 @@
       <c r="Y76" s="41"/>
       <c r="Z76" s="41"/>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A77" s="41"/>
       <c r="B77" s="41"/>
       <c r="C77" s="41"/>
@@ -6220,7 +6220,7 @@
       <c r="Y77" s="41"/>
       <c r="Z77" s="41"/>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A78" s="41"/>
       <c r="B78" s="41"/>
       <c r="C78" s="41"/>
@@ -6248,7 +6248,7 @@
       <c r="Y78" s="41"/>
       <c r="Z78" s="41"/>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A79" s="41"/>
       <c r="B79" s="41"/>
       <c r="C79" s="41"/>
@@ -6276,7 +6276,7 @@
       <c r="Y79" s="41"/>
       <c r="Z79" s="41"/>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A80" s="41"/>
       <c r="B80" s="41"/>
       <c r="C80" s="41"/>
@@ -6304,7 +6304,7 @@
       <c r="Y80" s="41"/>
       <c r="Z80" s="41"/>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A81" s="41"/>
       <c r="B81" s="41"/>
       <c r="C81" s="41"/>
@@ -6332,7 +6332,7 @@
       <c r="Y81" s="41"/>
       <c r="Z81" s="41"/>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A82" s="41"/>
       <c r="B82" s="41"/>
       <c r="C82" s="41"/>
@@ -6360,7 +6360,7 @@
       <c r="Y82" s="41"/>
       <c r="Z82" s="41"/>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A83" s="41"/>
       <c r="B83" s="41"/>
       <c r="C83" s="41"/>
@@ -6388,7 +6388,7 @@
       <c r="Y83" s="41"/>
       <c r="Z83" s="41"/>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A84" s="41"/>
       <c r="B84" s="41"/>
       <c r="C84" s="41"/>
@@ -6416,7 +6416,7 @@
       <c r="Y84" s="41"/>
       <c r="Z84" s="41"/>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A85" s="41"/>
       <c r="B85" s="41"/>
       <c r="C85" s="41"/>
@@ -6444,7 +6444,7 @@
       <c r="Y85" s="41"/>
       <c r="Z85" s="41"/>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A86" s="41"/>
       <c r="B86" s="41"/>
       <c r="C86" s="41"/>
@@ -6472,7 +6472,7 @@
       <c r="Y86" s="41"/>
       <c r="Z86" s="41"/>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A87" s="41"/>
       <c r="B87" s="41"/>
       <c r="C87" s="41"/>
@@ -6500,7 +6500,7 @@
       <c r="Y87" s="41"/>
       <c r="Z87" s="41"/>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A88" s="41"/>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -6528,7 +6528,7 @@
       <c r="Y88" s="41"/>
       <c r="Z88" s="41"/>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A89" s="41"/>
       <c r="B89" s="41"/>
       <c r="C89" s="41"/>
@@ -6556,7 +6556,7 @@
       <c r="Y89" s="41"/>
       <c r="Z89" s="41"/>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A90" s="41"/>
       <c r="B90" s="41"/>
       <c r="C90" s="41"/>
@@ -6584,7 +6584,7 @@
       <c r="Y90" s="41"/>
       <c r="Z90" s="41"/>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A91" s="41"/>
       <c r="B91" s="41"/>
       <c r="C91" s="41"/>
@@ -6612,7 +6612,7 @@
       <c r="Y91" s="41"/>
       <c r="Z91" s="41"/>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A92" s="41"/>
       <c r="B92" s="41"/>
       <c r="C92" s="41"/>
@@ -6640,7 +6640,7 @@
       <c r="Y92" s="41"/>
       <c r="Z92" s="41"/>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A93" s="41"/>
       <c r="B93" s="41"/>
       <c r="C93" s="41"/>
@@ -6668,7 +6668,7 @@
       <c r="Y93" s="41"/>
       <c r="Z93" s="41"/>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A94" s="41"/>
       <c r="B94" s="41"/>
       <c r="C94" s="41"/>
@@ -6696,7 +6696,7 @@
       <c r="Y94" s="41"/>
       <c r="Z94" s="41"/>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A95" s="41"/>
       <c r="B95" s="41"/>
       <c r="C95" s="41"/>
@@ -6724,7 +6724,7 @@
       <c r="Y95" s="41"/>
       <c r="Z95" s="41"/>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A96" s="41"/>
       <c r="B96" s="41"/>
       <c r="C96" s="41"/>
@@ -6752,7 +6752,7 @@
       <c r="Y96" s="41"/>
       <c r="Z96" s="41"/>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A97" s="41"/>
       <c r="B97" s="41"/>
       <c r="C97" s="41"/>
@@ -6780,7 +6780,7 @@
       <c r="Y97" s="41"/>
       <c r="Z97" s="41"/>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A98" s="41"/>
       <c r="B98" s="41"/>
       <c r="C98" s="41"/>
@@ -6808,7 +6808,7 @@
       <c r="Y98" s="41"/>
       <c r="Z98" s="41"/>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A99" s="41"/>
       <c r="B99" s="41"/>
       <c r="C99" s="41"/>
@@ -6860,35 +6860,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:AD37"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.109375" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="3" max="3" width="3.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" customWidth="1"/>
-    <col min="5" max="5" width="6.44140625" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.08984375" customWidth="1"/>
+    <col min="4" max="4" width="8.54296875" customWidth="1"/>
+    <col min="5" max="5" width="6.453125" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="5.44140625" customWidth="1"/>
-    <col min="10" max="11" width="5.6640625" customWidth="1"/>
-    <col min="12" max="12" width="6.5546875" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" customWidth="1"/>
+    <col min="9" max="9" width="5.453125" customWidth="1"/>
+    <col min="10" max="11" width="5.6328125" customWidth="1"/>
+    <col min="12" max="12" width="6.54296875" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.6640625" customWidth="1"/>
-    <col min="15" max="15" width="6.5546875" customWidth="1"/>
-    <col min="16" max="16" width="7.109375" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" customWidth="1"/>
+    <col min="14" max="14" width="6.6328125" customWidth="1"/>
+    <col min="15" max="15" width="6.54296875" customWidth="1"/>
+    <col min="16" max="16" width="7.08984375" customWidth="1"/>
+    <col min="17" max="17" width="5.6328125" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="5.88671875" customWidth="1"/>
-    <col min="20" max="20" width="5.5546875" customWidth="1"/>
-    <col min="21" max="21" width="5.88671875" customWidth="1"/>
-    <col min="22" max="22" width="6.6640625" customWidth="1"/>
+    <col min="19" max="19" width="5.90625" customWidth="1"/>
+    <col min="20" max="20" width="5.54296875" customWidth="1"/>
+    <col min="21" max="21" width="5.90625" customWidth="1"/>
+    <col min="22" max="22" width="6.6328125" customWidth="1"/>
     <col min="23" max="23" width="5" customWidth="1"/>
-    <col min="24" max="24" width="7.5546875" customWidth="1"/>
-    <col min="25" max="25" width="6.6640625" customWidth="1"/>
+    <col min="24" max="24" width="7.54296875" customWidth="1"/>
+    <col min="25" max="25" width="6.6328125" customWidth="1"/>
     <col min="26" max="28" width="6" customWidth="1"/>
-    <col min="29" max="29" width="5.6640625" customWidth="1"/>
-    <col min="30" max="30" width="6.6640625" customWidth="1"/>
+    <col min="29" max="29" width="5.6328125" customWidth="1"/>
+    <col min="30" max="30" width="6.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AD7" s="2"/>
     </row>
-    <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>64</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>118</v>
       </c>
@@ -7518,7 +7518,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>30480</xdr:colOff>
+                    <xdr:colOff>31750</xdr:colOff>
                     <xdr:row>3</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -7537,14 +7537,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A3:C39"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="1" max="2" width="11.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="10" t="s">
         <v>6</v>
@@ -7559,7 +7559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="8" t="s">
         <v>33</v>
@@ -7569,7 +7569,7 @@
         <v>IE</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="str">
@@ -7577,7 +7577,7 @@
         <v>National</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="str">
@@ -7585,7 +7585,7 @@
         <v>IE-CW</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8" t="str">
@@ -7593,7 +7593,7 @@
         <v>IE-D</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8" t="str">
@@ -7601,7 +7601,7 @@
         <v>IE-KE</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8" t="str">
@@ -7609,7 +7609,7 @@
         <v>IE-KK</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8" t="str">
@@ -7617,7 +7617,7 @@
         <v>IE-LS</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8" t="str">
@@ -7625,7 +7625,7 @@
         <v>IE-LD</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="8" t="str">
@@ -7633,7 +7633,7 @@
         <v>IE-LH</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8" t="str">
@@ -7641,7 +7641,7 @@
         <v>IE-MH</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="8" t="str">
@@ -7649,7 +7649,7 @@
         <v>IE-OY</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="8" t="str">
@@ -7657,7 +7657,7 @@
         <v>IE-WH</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8" t="str">
@@ -7665,7 +7665,7 @@
         <v>IE-WX</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="8" t="str">
@@ -7673,7 +7673,7 @@
         <v>IE-WW</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8" t="str">
@@ -7681,116 +7681,116 @@
         <v>IE-CE</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="C20" s="8" t="str">
         <f>Regions!R3</f>
         <v>IE-CO</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="C21" s="8" t="str">
         <f>Regions!S3</f>
         <v>IE-KY</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="C22" s="8" t="str">
         <f>Regions!T3</f>
         <v>IE-LK</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="C23" s="8" t="str">
         <f>Regions!U3</f>
         <v>IE-TA</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="C24" s="8" t="str">
         <f>Regions!V3</f>
         <v>IE-WD</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
       <c r="C25" s="8" t="str">
         <f>Regions!W3</f>
         <v>IE-G</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
       <c r="C26" s="8" t="str">
         <f>Regions!X3</f>
         <v>IE-LM</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="C27" s="8" t="str">
         <f>Regions!Y3</f>
         <v>IE-MO</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
       <c r="C28" s="8" t="str">
         <f>Regions!Z3</f>
         <v>IE-RN</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
       <c r="C29" s="8" t="str">
         <f>Regions!AA3</f>
         <v>IE-SO</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="C30" s="8" t="str">
         <f>Regions!AB3</f>
         <v>IE-CN</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A31" s="7"/>
       <c r="C31" s="8" t="str">
         <f>Regions!AC3</f>
         <v>IE-DL</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
       <c r="C32" s="8" t="str">
         <f>Regions!AD3</f>
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" ht="13" x14ac:dyDescent="0.3">
       <c r="A33" s="7"/>
     </row>
-    <row r="34" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" ht="13" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
     </row>
-    <row r="35" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" ht="13" x14ac:dyDescent="0.3">
       <c r="A35" s="7"/>
     </row>
-    <row r="36" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" ht="13" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
     </row>
-    <row r="37" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" ht="13" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
     </row>
-    <row r="38" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" ht="13" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
     </row>
-    <row r="39" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" ht="13" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
     </row>
   </sheetData>
@@ -7804,40 +7804,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B3:V51"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="9" width="13.6640625" customWidth="1"/>
+    <col min="2" max="9" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:22" ht="13" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="11"/>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2018</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" ht="13" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="11"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" ht="13" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="11"/>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>137</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>1</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B14" s="12">
         <v>1</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>1</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B16" s="12">
         <v>20</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B17" s="12">
         <v>20</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="C18" s="12">
         <v>5</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="C19" s="12">
         <v>45</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="C20" s="12">
         <v>25</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="C21" s="12">
         <v>5</v>
       </c>
@@ -8519,7 +8519,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="D22" s="12">
         <v>5</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="D23" s="12">
         <v>5</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="D24" s="12">
         <v>5</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="E25" s="12">
         <v>5</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="F26" s="12">
         <v>5</v>
       </c>
@@ -8788,7 +8788,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="F27" s="12">
         <v>5</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="G28" s="12">
         <v>5</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="G29" s="12">
         <v>5</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="G30" s="12">
         <v>5</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="G31" s="12">
         <v>5</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="G32" s="12">
         <v>5</v>
       </c>
@@ -8989,7 +8989,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="33" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="G33" s="12">
         <v>5</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="34" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="G34" s="12">
         <v>5</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="35" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="G35" s="12">
         <v>5</v>
       </c>
@@ -9079,7 +9079,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="36" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="H36" s="17">
         <v>1</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="37" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="H37" s="17">
         <v>1</v>
       </c>
@@ -9118,7 +9118,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="38" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="H38" s="17">
         <v>1</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="39" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="H39" s="17">
         <v>1</v>
       </c>
@@ -9150,7 +9150,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="40" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="H40" s="17">
         <v>1</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="41" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="H41" s="17">
         <v>1</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="42" spans="7:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
       <c r="H42" s="17">
         <v>1</v>
       </c>
@@ -9312,17 +9312,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B3:C9"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="52.6640625" customWidth="1"/>
+    <col min="2" max="2" width="52.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" ht="13" x14ac:dyDescent="0.3">
       <c r="B3" s="14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" ht="13" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
         <v>25</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B5" s="17" t="s">
         <v>27</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>28</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
         <v>29</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B8" s="12" t="s">
         <v>30</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" ht="13.25" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>49</v>
       </c>
@@ -9381,42 +9381,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:P24"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="6.44140625" customWidth="1"/>
-    <col min="8" max="8" width="6.33203125" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="6" max="6" width="10.6328125" customWidth="1"/>
+    <col min="7" max="7" width="6.453125" customWidth="1"/>
+    <col min="8" max="8" width="6.36328125" customWidth="1"/>
+    <col min="12" max="12" width="9.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22"/>
     </row>
-    <row r="2" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="O3" s="24"/>
       <c r="P3" s="24"/>
     </row>
-    <row r="4" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="O4" s="24"/>
       <c r="P4" s="24"/>
     </row>
-    <row r="5" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
     </row>
-    <row r="6" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
     </row>
-    <row r="7" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="O7" s="24"/>
       <c r="P7" s="24"/>
     </row>
-    <row r="8" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="24"/>
       <c r="B8" s="24"/>
       <c r="C8" s="24"/>
@@ -9434,7 +9434,7 @@
       <c r="O8" s="24"/>
       <c r="P8" s="24"/>
     </row>
-    <row r="9" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
@@ -9452,7 +9452,7 @@
       <c r="O9" s="24"/>
       <c r="P9" s="24"/>
     </row>
-    <row r="10" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="24"/>
       <c r="B10" s="24"/>
       <c r="C10" s="24"/>
@@ -9470,7 +9470,7 @@
       <c r="O10" s="24"/>
       <c r="P10" s="24"/>
     </row>
-    <row r="11" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="24"/>
       <c r="B11" s="24"/>
       <c r="C11" s="24"/>
@@ -9488,7 +9488,7 @@
       <c r="O11" s="24"/>
       <c r="P11" s="24"/>
     </row>
-    <row r="12" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A12" s="24"/>
       <c r="B12" s="24"/>
       <c r="C12" s="24"/>
@@ -9506,7 +9506,7 @@
       <c r="O12" s="24"/>
       <c r="P12" s="24"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="18" t="s">
         <v>52</v>
       </c>
@@ -9525,7 +9525,7 @@
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
     </row>
-    <row r="14" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>0</v>
       </c>
@@ -9595,7 +9595,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="24"/>
       <c r="B16" s="24"/>
       <c r="C16" s="24" t="s">
@@ -9621,7 +9621,7 @@
       <c r="O16" s="24"/>
       <c r="P16" s="24"/>
     </row>
-    <row r="17" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" s="24"/>
       <c r="B17" s="24"/>
       <c r="C17" s="24" t="s">
@@ -9647,7 +9647,7 @@
       <c r="O17" s="24"/>
       <c r="P17" s="24"/>
     </row>
-    <row r="18" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="24"/>
       <c r="B18" s="24"/>
       <c r="C18" s="24"/>
@@ -9665,7 +9665,7 @@
       <c r="O18" s="24"/>
       <c r="P18" s="24"/>
     </row>
-    <row r="19" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>11</v>
       </c>
@@ -9685,7 +9685,7 @@
       <c r="O19" s="24"/>
       <c r="P19" s="24"/>
     </row>
-    <row r="20" spans="1:16" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
         <v>12</v>
       </c>
@@ -9735,7 +9735,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
         <v>165</v>
       </c>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="P21" s="24"/>
     </row>
-    <row r="22" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" s="24"/>
       <c r="B22" s="24"/>
       <c r="C22" s="24" t="s">
@@ -9793,7 +9793,7 @@
       <c r="O22" s="24"/>
       <c r="P22" s="24"/>
     </row>
-    <row r="23" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="24"/>
       <c r="B23" s="24"/>
       <c r="C23" s="24"/>
@@ -9811,7 +9811,7 @@
       <c r="O23" s="24"/>
       <c r="P23" s="24"/>
     </row>
-    <row r="24" spans="1:16" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" s="24"/>
       <c r="B24" s="24"/>
       <c r="C24" s="24"/>
@@ -9840,22 +9840,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B1:G34"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
-    <col min="6" max="6" width="17.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" customWidth="1"/>
+    <col min="5" max="5" width="6.08984375" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="22" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
@@ -9880,7 +9880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="D5" s="7" t="s">
         <v>39</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B6" s="26"/>
       <c r="C6" s="26"/>
       <c r="D6" s="26" t="s">
@@ -9900,7 +9900,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B7" s="26"/>
       <c r="C7" s="26" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B3,4))</f>
@@ -9918,7 +9918,7 @@
         <v>1.3926669328933141</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B8" s="7"/>
       <c r="C8" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B4,4))</f>
@@ -9936,7 +9936,7 @@
         <v>1.3626878012654737</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B9" s="7"/>
       <c r="C9" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B5,4))</f>
@@ -9954,7 +9954,7 @@
         <v>1.3346599424735295</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B10" s="7"/>
       <c r="C10" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B6,4))</f>
@@ -9972,7 +9972,7 @@
         <v>1.3084901396799309</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B11" s="7"/>
       <c r="C11" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B7,4))</f>
@@ -9990,7 +9990,7 @@
         <v>1.2828334702744419</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="7"/>
       <c r="C12" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B8,4))</f>
@@ -10008,7 +10008,7 @@
         <v>1.2552186597597279</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B13" s="7"/>
       <c r="C13" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B9,4))</f>
@@ -10026,7 +10026,7 @@
         <v>1.2281982972208687</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B14" s="7"/>
       <c r="C14" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B10,4))</f>
@@ -10044,7 +10044,7 @@
         <v>1.2005848457682002</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B11,4))</f>
@@ -10062,7 +10062,7 @@
         <v>1.1577481637108971</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B16" s="7"/>
       <c r="C16" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B12,4))</f>
@@ -10080,7 +10080,7 @@
         <v>1.1462853106048485</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B17" s="7"/>
       <c r="C17" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B13,4))</f>
@@ -10098,7 +10098,7 @@
         <v>1.1227084335013209</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B18" s="7"/>
       <c r="C18" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B14,4))</f>
@@ -10116,7 +10116,7 @@
         <v>1.0889509539295061</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B19" s="7"/>
       <c r="C19" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B15,4))</f>
@@ -10134,7 +10134,7 @@
         <v>1.0613557055843141</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B20" s="7"/>
       <c r="C20" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B16,4))</f>
@@ -10152,7 +10152,7 @@
         <v>1.045670645895876</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B17,4))</f>
@@ -10170,7 +10170,7 @@
         <v>1.0394340416460002</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B22" s="7"/>
       <c r="C22" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B18,4))</f>
@@ -10188,7 +10188,7 @@
         <v>1.0383956459999999</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
       <c r="C23" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B19,4))</f>
@@ -10206,7 +10206,7 @@
         <v>1.0363230000000001</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
       <c r="C24" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B20,4))</f>
@@ -10224,7 +10224,7 @@
         <v>1.0190000000000001</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B25" s="7"/>
       <c r="C25" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B22,4))</f>
@@ -10242,7 +10242,7 @@
         <v>0.98522167487684731</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="C26" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B23,4))</f>
         <v>MEUR2020</v>
@@ -10259,7 +10259,7 @@
         <v>0.9783730634328176</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="C27" s="7" t="str">
         <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B24,4))</f>
         <v>MEUR2021</v>
@@ -10276,19 +10276,71 @@
         <v>0.95079986728164989</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="C28" s="7" t="str">
+        <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B25,4))</f>
+        <v>MEUR2022</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="25">
+        <f>CPI!$D$21/CPI!D25</f>
+        <v>0.87069584915901999</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="C29" s="7" t="str">
+        <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B26,4))</f>
+        <v>MEUR2023</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G29" s="25">
+        <f>CPI!$D$21/CPI!D26</f>
+        <v>0.81832316650283832</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="C30" s="7" t="str">
+        <f>_xlfn.CONCAT("MEUR",RIGHT(CPI!B27,4))</f>
+        <v>MEUR2024</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G30" s="25">
+        <f>CPI!$D$21/CPI!D27</f>
+        <v>0.79758593226397489</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B31" s="7"/>
     </row>
-    <row r="32" spans="2:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="13" x14ac:dyDescent="0.3">
       <c r="B32" s="7"/>
     </row>
-    <row r="33" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B33" s="7"/>
     </row>
-    <row r="34" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B34" s="25"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -10298,13 +10350,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="B2:O25"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:O29"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B2" s="10" t="s">
         <v>43</v>
       </c>
@@ -10353,7 +10405,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>161</v>
       </c>
@@ -10382,7 +10434,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="str">
         <f>Constants!C7</f>
         <v>MEUR2000</v>
@@ -10412,7 +10464,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="str">
         <f>Constants!C8</f>
         <v>MEUR2001</v>
@@ -10442,7 +10494,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="str">
         <f>Constants!C9</f>
         <v>MEUR2002</v>
@@ -10457,7 +10509,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="8" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="str">
         <f>Constants!C10</f>
         <v>MEUR2003</v>
@@ -10472,7 +10524,7 @@
         <v>41.87</v>
       </c>
     </row>
-    <row r="9" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="str">
         <f>Constants!C11</f>
         <v>MEUR2004</v>
@@ -10487,7 +10539,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="10" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="str">
         <f>Constants!C12</f>
         <v>MEUR2005</v>
@@ -10502,7 +10554,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="11" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="str">
         <f>Constants!C13</f>
         <v>MEUR2006</v>
@@ -10517,7 +10569,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="str">
         <f>Constants!C14</f>
         <v>MEUR2007</v>
@@ -10532,7 +10584,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="13" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="str">
         <f>Constants!C15</f>
         <v>MEUR2008</v>
@@ -10547,7 +10599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="str">
         <f>Constants!C16</f>
         <v>MEUR2009</v>
@@ -10562,7 +10614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="str">
         <f>Constants!C17</f>
         <v>MEUR2010</v>
@@ -10577,65 +10629,86 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" ht="13" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="str">
         <f>Constants!C18</f>
         <v>MEUR2011</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="str">
         <f>Constants!C19</f>
         <v>MEUR2012</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="str">
         <f>Constants!C20</f>
         <v>MEUR2013</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="str">
         <f>Constants!C21</f>
         <v>MEUR2014</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="str">
         <f>Constants!C22</f>
         <v>MEUR2015</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="str">
         <f>Constants!C23</f>
         <v>MEUR2016</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="str">
         <f>Constants!C24</f>
         <v>MEUR2017</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="str">
         <f>Constants!C25</f>
         <v>MEUR2019</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="str">
         <f>Constants!C26</f>
         <v>MEUR2020</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="str">
         <f>Constants!C27</f>
         <v>MEUR2021</v>
       </c>
+    </row>
+    <row r="26" spans="2:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="B26" s="7" t="str">
+        <f>Constants!C28</f>
+        <v>MEUR2022</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="B27" s="7" t="str">
+        <f>Constants!C29</f>
+        <v>MEUR2023</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="B28" s="7" t="str">
+        <f>Constants!C30</f>
+        <v>MEUR2024</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="B29" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10647,11 +10720,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="B2:D26"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:D32"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
-    <col min="3" max="4" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" customWidth="1"/>
+    <col min="3" max="4" width="13.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10663,7 +10736,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B3" s="31">
         <v>2000</v>
       </c>
@@ -10672,7 +10745,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B4" s="31">
         <v>2001</v>
       </c>
@@ -10684,7 +10757,7 @@
         <v>102.2</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B5" s="31">
         <v>2002</v>
       </c>
@@ -10696,7 +10769,7 @@
         <v>104.34620000000001</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B6" s="31">
         <v>2003</v>
       </c>
@@ -10708,7 +10781,7 @@
         <v>106.43312400000001</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B7" s="31">
         <v>2004</v>
       </c>
@@ -10720,7 +10793,7 @@
         <v>108.56178648000001</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B8" s="31">
         <v>2005</v>
       </c>
@@ -10732,7 +10805,7 @@
         <v>110.95014578256001</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B9" s="31">
         <v>2006</v>
       </c>
@@ -10744,7 +10817,7 @@
         <v>113.39104898977634</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B10" s="31">
         <v>2007</v>
       </c>
@@ -10756,7 +10829,7 @@
         <v>115.99904311654119</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B11" s="31">
         <v>2008</v>
       </c>
@@ -10768,7 +10841,7 @@
         <v>120.29100771185321</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B12" s="31">
         <v>2009</v>
       </c>
@@ -10780,7 +10853,7 @@
         <v>121.49391778897174</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B13" s="31">
         <v>2010</v>
       </c>
@@ -10792,7 +10865,7 @@
         <v>124.04529006254015</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B14" s="31">
         <v>2011</v>
       </c>
@@ -10804,7 +10877,7 @@
         <v>127.89069405447889</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B15" s="31">
         <v>2012</v>
       </c>
@@ -10816,7 +10889,7 @@
         <v>131.21585209989533</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B16" s="31">
         <v>2013</v>
       </c>
@@ -10828,7 +10901,7 @@
         <v>133.18408988139376</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B17" s="31">
         <v>2014</v>
       </c>
@@ -10840,7 +10913,7 @@
         <v>133.98319442068211</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B18" s="31">
         <v>2015</v>
       </c>
@@ -10852,7 +10925,7 @@
         <v>134.1171776151028</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B19" s="36">
         <v>2016</v>
       </c>
@@ -10864,7 +10937,7 @@
         <v>134.385411970333</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B20" s="36">
         <v>2017</v>
       </c>
@@ -10876,7 +10949,7 @@
         <v>136.66996397382866</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B21" s="36">
         <v>2018</v>
       </c>
@@ -10888,7 +10961,7 @@
         <v>139.26669328933141</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B22" s="36">
         <v>2019</v>
       </c>
@@ -10900,7 +10973,7 @@
         <v>141.35569368867138</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B23" s="36">
         <v>2020</v>
       </c>
@@ -10912,7 +10985,7 @@
         <v>142.34518354449207</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="B24" s="36">
         <v>2021</v>
       </c>
@@ -10924,8 +10997,54 @@
         <v>146.47319386728233</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B26" s="35" t="s">
+    <row r="25" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="B25" s="36">
+        <v>2022</v>
+      </c>
+      <c r="C25" s="38">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="D25" s="37">
+        <f t="shared" ref="D25:D27" si="3">D24+D24*C25</f>
+        <v>159.94872770307231</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="B26" s="36">
+        <v>2023</v>
+      </c>
+      <c r="C26" s="38">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="D26" s="37">
+        <f t="shared" si="3"/>
+        <v>170.18544627606894</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="B27" s="36">
+        <v>2024</v>
+      </c>
+      <c r="C27" s="38">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="D27" s="37">
+        <f t="shared" si="3"/>
+        <v>174.61026787924675</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="B28" s="36"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="37"/>
+    </row>
+    <row r="29" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="B29" s="36"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="37"/>
+    </row>
+    <row r="32" spans="2:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="B32" s="35" t="s">
         <v>36</v>
       </c>
     </row>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BB1EBD-AD17-47CD-994B-6C52298E6487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D7E432-BBD3-4827-B824-DED810952E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="28" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="170">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="C3" s="11"/>
     </row>
-    <row r="4" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2018</v>
       </c>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="C7" s="11"/>
     </row>
-    <row r="8" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>37</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="13" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>1</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="14" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="12">
         <v>1</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>1</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="12">
         <v>20</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="17" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B17" s="12">
         <v>20</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="18" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C18" s="12">
         <v>5</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="19" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C19" s="12">
         <v>45</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="20" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C20" s="12">
         <v>25</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C21" s="12">
         <v>5</v>
       </c>
@@ -8519,7 +8519,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="22" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
       <c r="D22" s="12">
         <v>5</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="23" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
       <c r="D23" s="12">
         <v>5</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="24" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
       <c r="D24" s="12">
         <v>5</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="25" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="E25" s="12">
         <v>5</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="26" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="F26" s="12">
         <v>5</v>
       </c>
@@ -8788,7 +8788,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="27" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="F27" s="12">
         <v>5</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="28" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="G28" s="12">
         <v>5</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="29" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="G29" s="12">
         <v>5</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="30" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="G30" s="12">
         <v>5</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="31" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
       <c r="G31" s="12">
         <v>5</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="32" spans="2:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
       <c r="G32" s="12">
         <v>5</v>
       </c>
@@ -8989,7 +8989,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="33" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:22" x14ac:dyDescent="0.25">
       <c r="G33" s="12">
         <v>5</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="34" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:22" x14ac:dyDescent="0.25">
       <c r="G34" s="12">
         <v>5</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="35" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:22" x14ac:dyDescent="0.25">
       <c r="G35" s="12">
         <v>5</v>
       </c>
@@ -9079,7 +9079,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="36" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H36" s="17">
         <v>1</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="37" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H37" s="17">
         <v>1</v>
       </c>
@@ -9118,7 +9118,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="38" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H38" s="17">
         <v>1</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="39" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H39" s="17">
         <v>1</v>
       </c>
@@ -9150,7 +9150,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="40" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H40" s="17">
         <v>1</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="41" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H41" s="17">
         <v>1</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="42" spans="7:22" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:22" x14ac:dyDescent="0.25">
       <c r="H42" s="17">
         <v>1</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="17" t="s">
         <v>27</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>28</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
         <v>29</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="12" t="s">
         <v>30</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="13.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>49</v>
       </c>
@@ -9784,7 +9784,7 @@
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
       <c r="J22" s="24" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K22" s="24"/>
       <c r="L22" s="24"/>
@@ -9796,14 +9796,22 @@
     <row r="23" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="24"/>
       <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
+      <c r="C23" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="24">
+        <v>0</v>
+      </c>
       <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
+      <c r="F23" s="24">
+        <v>5</v>
+      </c>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
       <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
+      <c r="J23" s="24" t="s">
+        <v>1</v>
+      </c>
       <c r="K23" s="24"/>
       <c r="L23" s="24"/>
       <c r="M23" s="24"/>
